--- a/jogos_2026-06-01.xlsx
+++ b/jogos_2026-06-01.xlsx
@@ -1160,7 +1160,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Macará</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1319,7 +1319,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Macará</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,13 +1361,13 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Curicó Unido</t>
+          <t>Barra do Garcas</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Barra do Garcas</t>
+          <t>Curicó Unido</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2156,13 +2156,13 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>

--- a/jogos_2026-06-01.xlsx
+++ b/jogos_2026-06-01.xlsx
@@ -1160,7 +1160,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Macará</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -1319,7 +1319,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Macará</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,13 +1361,13 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>

--- a/jogos_2026-06-01.xlsx
+++ b/jogos_2026-06-01.xlsx
@@ -1160,7 +1160,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Macará</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -1319,7 +1319,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Macará</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,13 +1361,13 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Barra do Garcas</t>
+          <t>Curicó Unido</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Curicó Unido</t>
+          <t>Deportes Santa Cruz</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Copiapó</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Deportes Santa Cruz</t>
+          <t>Barra do Garcas</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Copiapó</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="G9" t="n">

--- a/jogos_2026-06-01.xlsx
+++ b/jogos_2026-06-01.xlsx
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Deportes Santa Cruz</t>
+          <t>Barra do Garcas</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Copiapó</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Barra do Garcas</t>
+          <t>Deportes Santa Cruz</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Copiapó</t>
         </is>
       </c>
       <c r="G9" t="n">

--- a/jogos_2026-06-01.xlsx
+++ b/jogos_2026-06-01.xlsx
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Curicó Unido</t>
+          <t>Barra do Garcas</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Barra do Garcas</t>
+          <t>Deportes Santa Cruz</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Copiapó</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Deportes Santa Cruz</t>
+          <t>Curicó Unido</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Copiapó</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="G9" t="n">

--- a/jogos_2026-06-01.xlsx
+++ b/jogos_2026-06-01.xlsx
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Barra do Garcas</t>
+          <t>Deportes Santa Cruz</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Copiapó</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Deportes Santa Cruz</t>
+          <t>Curicó Unido</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Copiapó</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Curicó Unido</t>
+          <t>Barra do Garcas</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="G9" t="n">

--- a/jogos_2026-06-01.xlsx
+++ b/jogos_2026-06-01.xlsx
@@ -1160,7 +1160,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Macará</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>2.42</v>
+        <v>3.15</v>
       </c>
       <c r="O5" t="n">
-        <v>2.89</v>
+        <v>2.9</v>
       </c>
       <c r="P5" t="n">
-        <v>3.18</v>
+        <v>2.25</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -1319,7 +1319,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Macará</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,13 +1361,13 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>3.15</v>
+        <v>2.42</v>
       </c>
       <c r="O6" t="n">
-        <v>2.9</v>
+        <v>2.89</v>
       </c>
       <c r="P6" t="n">
-        <v>2.25</v>
+        <v>3.18</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Curicó Unido</t>
+          <t>Barra do Garcas</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Barra do Garcas</t>
+          <t>Curicó Unido</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="G9" t="n">

--- a/jogos_2026-06-01.xlsx
+++ b/jogos_2026-06-01.xlsx
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Deportes Santa Cruz</t>
+          <t>Curicó Unido</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Copiapó</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Barra do Garcas</t>
+          <t>Deportes Santa Cruz</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Copiapó</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Curicó Unido</t>
+          <t>Barra do Garcas</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="G9" t="n">

--- a/jogos_2026-06-01.xlsx
+++ b/jogos_2026-06-01.xlsx
@@ -1160,7 +1160,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Macará</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>3.15</v>
+        <v>2.42</v>
       </c>
       <c r="O5" t="n">
-        <v>2.9</v>
+        <v>2.89</v>
       </c>
       <c r="P5" t="n">
-        <v>2.25</v>
+        <v>3.18</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -1319,7 +1319,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Macará</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,13 +1361,13 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>2.42</v>
+        <v>3.15</v>
       </c>
       <c r="O6" t="n">
-        <v>2.89</v>
+        <v>2.9</v>
       </c>
       <c r="P6" t="n">
-        <v>3.18</v>
+        <v>2.25</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Curicó Unido</t>
+          <t>Deportes Santa Cruz</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Copiapó</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Deportes Santa Cruz</t>
+          <t>Barra do Garcas</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Copiapó</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Barra do Garcas</t>
+          <t>Curicó Unido</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="G9" t="n">

--- a/jogos_2026-06-01.xlsx
+++ b/jogos_2026-06-01.xlsx
@@ -1160,7 +1160,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Macará</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>2.42</v>
+        <v>3.15</v>
       </c>
       <c r="O5" t="n">
-        <v>2.89</v>
+        <v>2.9</v>
       </c>
       <c r="P5" t="n">
-        <v>3.18</v>
+        <v>2.25</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -1319,7 +1319,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Macará</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,13 +1361,13 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>3.15</v>
+        <v>2.42</v>
       </c>
       <c r="O6" t="n">
-        <v>2.9</v>
+        <v>2.89</v>
       </c>
       <c r="P6" t="n">
-        <v>2.25</v>
+        <v>3.18</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Deportes Santa Cruz</t>
+          <t>Curicó Unido</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Copiapó</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Curicó Unido</t>
+          <t>Deportes Santa Cruz</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Copiapó</t>
         </is>
       </c>
       <c r="G9" t="n">

--- a/jogos_2026-06-01.xlsx
+++ b/jogos_2026-06-01.xlsx
@@ -1160,7 +1160,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Macará</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>3.15</v>
+        <v>2.42</v>
       </c>
       <c r="O5" t="n">
-        <v>2.9</v>
+        <v>2.89</v>
       </c>
       <c r="P5" t="n">
-        <v>2.25</v>
+        <v>3.18</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -1319,7 +1319,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Macará</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,13 +1361,13 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>2.42</v>
+        <v>3.15</v>
       </c>
       <c r="O6" t="n">
-        <v>2.89</v>
+        <v>2.9</v>
       </c>
       <c r="P6" t="n">
-        <v>3.18</v>
+        <v>2.25</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Curicó Unido</t>
+          <t>Barra do Garcas</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Barra do Garcas</t>
+          <t>Curicó Unido</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="G8" t="n">

--- a/jogos_2026-06-01.xlsx
+++ b/jogos_2026-06-01.xlsx
@@ -1160,7 +1160,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Macará</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>2.42</v>
+        <v>3.15</v>
       </c>
       <c r="O5" t="n">
-        <v>2.89</v>
+        <v>2.9</v>
       </c>
       <c r="P5" t="n">
-        <v>3.18</v>
+        <v>2.25</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -1319,7 +1319,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Macará</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,13 +1361,13 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>3.15</v>
+        <v>2.42</v>
       </c>
       <c r="O6" t="n">
-        <v>2.9</v>
+        <v>2.89</v>
       </c>
       <c r="P6" t="n">
-        <v>2.25</v>
+        <v>3.18</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>

--- a/jogos_2026-06-01.xlsx
+++ b/jogos_2026-06-01.xlsx
@@ -1160,7 +1160,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Macará</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>3.15</v>
+        <v>2.42</v>
       </c>
       <c r="O5" t="n">
-        <v>2.9</v>
+        <v>2.89</v>
       </c>
       <c r="P5" t="n">
-        <v>2.25</v>
+        <v>3.18</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -1319,7 +1319,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Macará</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,13 +1361,13 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>2.42</v>
+        <v>3.15</v>
       </c>
       <c r="O6" t="n">
-        <v>2.89</v>
+        <v>2.9</v>
       </c>
       <c r="P6" t="n">
-        <v>3.18</v>
+        <v>2.25</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Barra do Garcas</t>
+          <t>Curicó Unido</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Curicó Unido</t>
+          <t>Deportes Santa Cruz</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Copiapó</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Deportes Santa Cruz</t>
+          <t>Barra do Garcas</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Copiapó</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="G9" t="n">

--- a/jogos_2026-06-01.xlsx
+++ b/jogos_2026-06-01.xlsx
@@ -1160,7 +1160,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Macará</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>2.42</v>
+        <v>3.15</v>
       </c>
       <c r="O5" t="n">
-        <v>2.89</v>
+        <v>2.9</v>
       </c>
       <c r="P5" t="n">
-        <v>3.18</v>
+        <v>2.25</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -1319,7 +1319,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Macará</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,13 +1361,13 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>3.15</v>
+        <v>2.42</v>
       </c>
       <c r="O6" t="n">
-        <v>2.9</v>
+        <v>2.89</v>
       </c>
       <c r="P6" t="n">
-        <v>2.25</v>
+        <v>3.18</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Curicó Unido</t>
+          <t>Deportes Santa Cruz</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Copiapó</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Deportes Santa Cruz</t>
+          <t>Barra do Garcas</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Copiapó</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Barra do Garcas</t>
+          <t>Curicó Unido</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="G9" t="n">

--- a/jogos_2026-06-01.xlsx
+++ b/jogos_2026-06-01.xlsx
@@ -1160,7 +1160,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Macará</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>3.15</v>
+        <v>2.42</v>
       </c>
       <c r="O5" t="n">
-        <v>2.9</v>
+        <v>2.89</v>
       </c>
       <c r="P5" t="n">
-        <v>2.25</v>
+        <v>3.18</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -1319,7 +1319,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Macará</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,13 +1361,13 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>2.42</v>
+        <v>3.15</v>
       </c>
       <c r="O6" t="n">
-        <v>2.89</v>
+        <v>2.9</v>
       </c>
       <c r="P6" t="n">
-        <v>3.18</v>
+        <v>2.25</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Deportes Santa Cruz</t>
+          <t>Curicó Unido</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Copiapó</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Barra do Garcas</t>
+          <t>Deportes Santa Cruz</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Copiapó</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Curicó Unido</t>
+          <t>Barra do Garcas</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,13 +1838,13 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>

--- a/jogos_2026-06-01.xlsx
+++ b/jogos_2026-06-01.xlsx
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Curicó Unido</t>
+          <t>Deportes Santa Cruz</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Copiapó</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Deportes Santa Cruz</t>
+          <t>Barra do Garcas</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Copiapó</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Barra do Garcas</t>
+          <t>Curicó Unido</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,13 +1838,13 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>

--- a/jogos_2026-06-01.xlsx
+++ b/jogos_2026-06-01.xlsx
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Deportes Santa Cruz</t>
+          <t>Curicó Unido</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Copiapó</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Barra do Garcas</t>
+          <t>Deportes Santa Cruz</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Copiapó</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Curicó Unido</t>
+          <t>Barra do Garcas</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,13 +1838,13 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>

--- a/jogos_2026-06-01.xlsx
+++ b/jogos_2026-06-01.xlsx
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Deportes Santa Cruz</t>
+          <t>Barra do Garcas</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Copiapó</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Barra do Garcas</t>
+          <t>Deportes Santa Cruz</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Copiapó</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,13 +1838,13 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>

--- a/jogos_2026-06-01.xlsx
+++ b/jogos_2026-06-01.xlsx
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Curicó Unido</t>
+          <t>Deportes Santa Cruz</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Copiapó</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Deportes Santa Cruz</t>
+          <t>Curicó Unido</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Copiapó</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="G9" t="n">

--- a/jogos_2026-06-01.xlsx
+++ b/jogos_2026-06-01.xlsx
@@ -1160,7 +1160,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Macará</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>2.42</v>
+        <v>3.15</v>
       </c>
       <c r="O5" t="n">
-        <v>2.89</v>
+        <v>2.9</v>
       </c>
       <c r="P5" t="n">
-        <v>3.18</v>
+        <v>2.25</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -1319,7 +1319,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Macará</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,13 +1361,13 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>3.15</v>
+        <v>2.42</v>
       </c>
       <c r="O6" t="n">
-        <v>2.9</v>
+        <v>2.89</v>
       </c>
       <c r="P6" t="n">
-        <v>2.25</v>
+        <v>3.18</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Deportes Santa Cruz</t>
+          <t>Barra do Garcas</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Copiapó</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Barra do Garcas</t>
+          <t>Curicó Unido</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Curicó Unido</t>
+          <t>Deportes Santa Cruz</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Copiapó</t>
         </is>
       </c>
       <c r="G9" t="n">

--- a/jogos_2026-06-01.xlsx
+++ b/jogos_2026-06-01.xlsx
@@ -1160,7 +1160,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Macará</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>3.15</v>
+        <v>2.42</v>
       </c>
       <c r="O5" t="n">
-        <v>2.9</v>
+        <v>2.89</v>
       </c>
       <c r="P5" t="n">
-        <v>2.25</v>
+        <v>3.18</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -1319,7 +1319,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Macará</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,13 +1361,13 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>2.42</v>
+        <v>3.15</v>
       </c>
       <c r="O6" t="n">
-        <v>2.89</v>
+        <v>2.9</v>
       </c>
       <c r="P6" t="n">
-        <v>3.18</v>
+        <v>2.25</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Barra do Garcas</t>
+          <t>Deportes Santa Cruz</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Copiapó</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Deportes Santa Cruz</t>
+          <t>Barra do Garcas</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Copiapó</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,13 +1838,13 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>

--- a/jogos_2026-06-01.xlsx
+++ b/jogos_2026-06-01.xlsx
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Curicó Unido</t>
+          <t>Barra do Garcas</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Barra do Garcas</t>
+          <t>Curicó Unido</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,13 +1838,13 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>

--- a/jogos_2026-06-01.xlsx
+++ b/jogos_2026-06-01.xlsx
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Deportes Santa Cruz</t>
+          <t>Barra do Garcas</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Copiapó</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Barra do Garcas</t>
+          <t>Curicó Unido</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Curicó Unido</t>
+          <t>Deportes Santa Cruz</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Copiapó</t>
         </is>
       </c>
       <c r="G9" t="n">

--- a/jogos_2026-06-01.xlsx
+++ b/jogos_2026-06-01.xlsx
@@ -1160,7 +1160,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Macará</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>2.42</v>
+        <v>3.15</v>
       </c>
       <c r="O5" t="n">
-        <v>2.89</v>
+        <v>2.9</v>
       </c>
       <c r="P5" t="n">
-        <v>3.18</v>
+        <v>2.25</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -1319,7 +1319,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Macará</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,13 +1361,13 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>3.15</v>
+        <v>2.42</v>
       </c>
       <c r="O6" t="n">
-        <v>2.9</v>
+        <v>2.89</v>
       </c>
       <c r="P6" t="n">
-        <v>2.25</v>
+        <v>3.18</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Barra do Garcas</t>
+          <t>Curicó Unido</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Curicó Unido</t>
+          <t>Deportes Santa Cruz</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Copiapó</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Deportes Santa Cruz</t>
+          <t>Barra do Garcas</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Copiapó</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,13 +1838,13 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>

--- a/jogos_2026-06-01.xlsx
+++ b/jogos_2026-06-01.xlsx
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Curicó Unido</t>
+          <t>Barra do Garcas</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Deportes Santa Cruz</t>
+          <t>Curicó Unido</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Copiapó</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Barra do Garcas</t>
+          <t>Deportes Santa Cruz</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Copiapó</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,13 +1838,13 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>

--- a/jogos_2026-06-01.xlsx
+++ b/jogos_2026-06-01.xlsx
@@ -884,13 +884,13 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -1160,7 +1160,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Macará</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>3.15</v>
+        <v>2.42</v>
       </c>
       <c r="O5" t="n">
-        <v>2.9</v>
+        <v>2.89</v>
       </c>
       <c r="P5" t="n">
-        <v>2.25</v>
+        <v>3.18</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -1319,7 +1319,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Macará</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,13 +1361,13 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>2.42</v>
+        <v>3.15</v>
       </c>
       <c r="O6" t="n">
-        <v>2.89</v>
+        <v>2.9</v>
       </c>
       <c r="P6" t="n">
-        <v>3.18</v>
+        <v>2.25</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>

--- a/jogos_2026-06-01.xlsx
+++ b/jogos_2026-06-01.xlsx
@@ -1160,7 +1160,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Macará</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>2.42</v>
+        <v>3.15</v>
       </c>
       <c r="O5" t="n">
-        <v>2.89</v>
+        <v>2.9</v>
       </c>
       <c r="P5" t="n">
-        <v>3.18</v>
+        <v>2.25</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -1319,7 +1319,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Macará</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,13 +1361,13 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>3.15</v>
+        <v>2.42</v>
       </c>
       <c r="O6" t="n">
-        <v>2.9</v>
+        <v>2.89</v>
       </c>
       <c r="P6" t="n">
-        <v>2.25</v>
+        <v>3.18</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Deportes Santa Cruz</t>
+          <t>Barra do Garcas</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Copiapó</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Barra do Garcas</t>
+          <t>Deportes Santa Cruz</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Copiapó</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,13 +1838,13 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>

--- a/jogos_2026-06-01.xlsx
+++ b/jogos_2026-06-01.xlsx
@@ -1160,7 +1160,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Macará</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>3.15</v>
+        <v>2.42</v>
       </c>
       <c r="O5" t="n">
-        <v>2.9</v>
+        <v>2.89</v>
       </c>
       <c r="P5" t="n">
-        <v>2.25</v>
+        <v>3.18</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -1319,7 +1319,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Macará</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,13 +1361,13 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>2.42</v>
+        <v>3.15</v>
       </c>
       <c r="O6" t="n">
-        <v>2.89</v>
+        <v>2.9</v>
       </c>
       <c r="P6" t="n">
-        <v>3.18</v>
+        <v>2.25</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Barra do Garcas</t>
+          <t>Deportes Santa Cruz</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Copiapó</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Curicó Unido</t>
+          <t>Barra do Garcas</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Deportes Santa Cruz</t>
+          <t>Curicó Unido</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Copiapó</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="G9" t="n">

--- a/jogos_2026-06-01.xlsx
+++ b/jogos_2026-06-01.xlsx
@@ -1043,13 +1043,13 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -1211,55 +1211,55 @@
         <v>3.18</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AK5" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1370,55 +1370,55 @@
         <v>2.25</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AK6" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Deportes Santa Cruz</t>
+          <t>Curicó Unido</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Copiapó</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1.91</v>
+        <v>2.1</v>
       </c>
       <c r="O8" t="n">
-        <v>3</v>
+        <v>2.87</v>
       </c>
       <c r="P8" t="n">
-        <v>3.9</v>
+        <v>3.6</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Curicó Unido</t>
+          <t>Deportes Santa Cruz</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Copiapó</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,13 +1838,13 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
@@ -2156,64 +2156,64 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>2.85</v>
+        <v>2.95</v>
       </c>
       <c r="O11" t="n">
-        <v>2.85</v>
+        <v>2.93</v>
       </c>
       <c r="P11" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AK11" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>

--- a/jogos_2026-06-01.xlsx
+++ b/jogos_2026-06-01.xlsx
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Curicó Unido</t>
+          <t>Deportes Santa Cruz</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Copiapó</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>2.63</v>
+        <v>2.12</v>
       </c>
       <c r="O7" t="n">
-        <v>3.35</v>
+        <v>3.15</v>
       </c>
       <c r="P7" t="n">
-        <v>2.3</v>
+        <v>3.1</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Deportes Santa Cruz</t>
+          <t>Curicó Unido</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Copiapó</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,13 +1838,13 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>2.12</v>
+        <v>2.63</v>
       </c>
       <c r="O9" t="n">
-        <v>3.15</v>
+        <v>3.35</v>
       </c>
       <c r="P9" t="n">
-        <v>3.1</v>
+        <v>2.3</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>

--- a/jogos_2026-06-01.xlsx
+++ b/jogos_2026-06-01.xlsx
@@ -1160,7 +1160,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Macará</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,64 +1202,64 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>2.42</v>
+        <v>3.15</v>
       </c>
       <c r="O5" t="n">
-        <v>2.89</v>
+        <v>2.9</v>
       </c>
       <c r="P5" t="n">
-        <v>3.18</v>
+        <v>2.25</v>
       </c>
       <c r="Q5" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="S5" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="U5" t="n">
         <v>3.4</v>
-      </c>
-      <c r="R5" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="S5" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="T5" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="U5" t="n">
-        <v>3.3</v>
       </c>
       <c r="V5" t="n">
         <v>1.24</v>
       </c>
       <c r="W5" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="X5" t="n">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.65</v>
+        <v>2.45</v>
       </c>
       <c r="AA5" t="n">
         <v>2.45</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.57</v>
+        <v>1.51</v>
       </c>
       <c r="AC5" t="n">
         <v>4.8</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.93</v>
+        <v>2.17</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AK5" t="n">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1319,7 +1319,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Macará</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,64 +1361,64 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>3.15</v>
+        <v>2.42</v>
       </c>
       <c r="O6" t="n">
-        <v>2.9</v>
+        <v>2.89</v>
       </c>
       <c r="P6" t="n">
-        <v>2.25</v>
+        <v>3.18</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.8</v>
+        <v>3.4</v>
       </c>
       <c r="R6" t="n">
-        <v>1.95</v>
+        <v>2.02</v>
       </c>
       <c r="S6" t="n">
-        <v>1.5</v>
+        <v>1.56</v>
       </c>
       <c r="T6" t="n">
-        <v>2.28</v>
+        <v>2.31</v>
       </c>
       <c r="U6" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="V6" t="n">
         <v>1.24</v>
       </c>
       <c r="W6" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="X6" t="n">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.45</v>
+        <v>2.65</v>
       </c>
       <c r="AA6" t="n">
         <v>2.45</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.51</v>
+        <v>1.57</v>
       </c>
       <c r="AC6" t="n">
         <v>4.8</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="AF6" t="n">
-        <v>2.17</v>
+        <v>1.93</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.3</v>
+        <v>1.44</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>

--- a/jogos_2026-06-01.xlsx
+++ b/jogos_2026-06-01.xlsx
@@ -1160,7 +1160,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Macará</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,64 +1202,64 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>3.15</v>
+        <v>2.42</v>
       </c>
       <c r="O5" t="n">
-        <v>2.9</v>
+        <v>2.89</v>
       </c>
       <c r="P5" t="n">
-        <v>2.25</v>
+        <v>3.18</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.8</v>
+        <v>3.35</v>
       </c>
       <c r="R5" t="n">
-        <v>1.95</v>
+        <v>2.02</v>
       </c>
       <c r="S5" t="n">
-        <v>1.5</v>
+        <v>1.56</v>
       </c>
       <c r="T5" t="n">
-        <v>2.28</v>
+        <v>2.31</v>
       </c>
       <c r="U5" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="V5" t="n">
         <v>1.24</v>
       </c>
       <c r="W5" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="X5" t="n">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.45</v>
+        <v>2.6</v>
       </c>
       <c r="AA5" t="n">
         <v>2.45</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="AC5" t="n">
         <v>4.8</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="AF5" t="n">
-        <v>2.17</v>
+        <v>2</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AK5" t="n">
-        <v>1.3</v>
+        <v>1.44</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1319,7 +1319,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Macará</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,64 +1361,64 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>2.42</v>
+        <v>3.15</v>
       </c>
       <c r="O6" t="n">
-        <v>2.89</v>
+        <v>2.9</v>
       </c>
       <c r="P6" t="n">
-        <v>3.18</v>
+        <v>2.25</v>
       </c>
       <c r="Q6" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="S6" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="T6" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="U6" t="n">
         <v>3.4</v>
-      </c>
-      <c r="R6" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="S6" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="T6" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="U6" t="n">
-        <v>3.3</v>
       </c>
       <c r="V6" t="n">
         <v>1.24</v>
       </c>
       <c r="W6" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="X6" t="n">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.65</v>
+        <v>2.45</v>
       </c>
       <c r="AA6" t="n">
         <v>2.45</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.57</v>
+        <v>1.51</v>
       </c>
       <c r="AC6" t="n">
         <v>4.8</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.93</v>
+        <v>2.17</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Deportes Santa Cruz</t>
+          <t>Barra do Garcas</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Copiapó</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="O7" t="n">
-        <v>3.15</v>
+        <v>2.87</v>
       </c>
       <c r="P7" t="n">
-        <v>3.1</v>
+        <v>3.6</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Barra do Garcas</t>
+          <t>Curicó Unido</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>2.1</v>
+        <v>2.63</v>
       </c>
       <c r="O8" t="n">
-        <v>2.87</v>
+        <v>3.35</v>
       </c>
       <c r="P8" t="n">
-        <v>3.6</v>
+        <v>2.3</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Curicó Unido</t>
+          <t>Deportes Santa Cruz</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Copiapó</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,13 +1838,13 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>2.63</v>
+        <v>2.12</v>
       </c>
       <c r="O9" t="n">
-        <v>3.35</v>
+        <v>3.15</v>
       </c>
       <c r="P9" t="n">
-        <v>2.3</v>
+        <v>3.1</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>

--- a/jogos_2026-06-01.xlsx
+++ b/jogos_2026-06-01.xlsx
@@ -1160,7 +1160,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Macará</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,64 +1202,64 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>2.42</v>
+        <v>3.15</v>
       </c>
       <c r="O5" t="n">
-        <v>2.89</v>
+        <v>2.9</v>
       </c>
       <c r="P5" t="n">
-        <v>3.18</v>
+        <v>2.25</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.35</v>
+        <v>3.8</v>
       </c>
       <c r="R5" t="n">
-        <v>2.02</v>
+        <v>1.95</v>
       </c>
       <c r="S5" t="n">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="T5" t="n">
-        <v>2.31</v>
+        <v>2.28</v>
       </c>
       <c r="U5" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="V5" t="n">
         <v>1.24</v>
       </c>
       <c r="W5" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="X5" t="n">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.48</v>
+        <v>1.53</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.6</v>
+        <v>2.45</v>
       </c>
       <c r="AA5" t="n">
         <v>2.45</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="AC5" t="n">
         <v>4.8</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="AF5" t="n">
-        <v>2</v>
+        <v>2.17</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AK5" t="n">
-        <v>1.44</v>
+        <v>1.31</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1319,7 +1319,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Macará</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,64 +1361,64 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>3.15</v>
+        <v>2.42</v>
       </c>
       <c r="O6" t="n">
-        <v>2.9</v>
+        <v>2.89</v>
       </c>
       <c r="P6" t="n">
-        <v>2.25</v>
+        <v>3.18</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.8</v>
+        <v>3.35</v>
       </c>
       <c r="R6" t="n">
-        <v>1.95</v>
+        <v>2.02</v>
       </c>
       <c r="S6" t="n">
-        <v>1.5</v>
+        <v>1.56</v>
       </c>
       <c r="T6" t="n">
-        <v>2.28</v>
+        <v>2.31</v>
       </c>
       <c r="U6" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="V6" t="n">
         <v>1.24</v>
       </c>
       <c r="W6" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="X6" t="n">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.45</v>
+        <v>2.6</v>
       </c>
       <c r="AA6" t="n">
         <v>2.45</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="AC6" t="n">
         <v>4.8</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="AF6" t="n">
-        <v>2.17</v>
+        <v>2</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.3</v>
+        <v>1.44</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Barra do Garcas</t>
+          <t>Curicó Unido</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>2.1</v>
+        <v>2.63</v>
       </c>
       <c r="O7" t="n">
-        <v>2.87</v>
+        <v>3.35</v>
       </c>
       <c r="P7" t="n">
-        <v>3.6</v>
+        <v>2.3</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Curicó Unido</t>
+          <t>Barra do Garcas</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>2.63</v>
+        <v>2.15</v>
       </c>
       <c r="O8" t="n">
-        <v>3.35</v>
+        <v>2.89</v>
       </c>
       <c r="P8" t="n">
-        <v>2.3</v>
+        <v>3.6</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -2159,7 +2159,7 @@
         <v>2.95</v>
       </c>
       <c r="O11" t="n">
-        <v>2.93</v>
+        <v>2.9</v>
       </c>
       <c r="P11" t="n">
         <v>2.3</v>
@@ -2198,7 +2198,7 @@
         <v>2.49</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AC11" t="n">
         <v>4.8</v>

--- a/jogos_2026-06-01.xlsx
+++ b/jogos_2026-06-01.xlsx
@@ -1160,7 +1160,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Macará</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,64 +1202,64 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>3.15</v>
+        <v>2.42</v>
       </c>
       <c r="O5" t="n">
-        <v>2.9</v>
+        <v>2.89</v>
       </c>
       <c r="P5" t="n">
-        <v>2.25</v>
+        <v>3.18</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.8</v>
+        <v>3.35</v>
       </c>
       <c r="R5" t="n">
-        <v>1.95</v>
+        <v>2.02</v>
       </c>
       <c r="S5" t="n">
-        <v>1.5</v>
+        <v>1.56</v>
       </c>
       <c r="T5" t="n">
-        <v>2.28</v>
+        <v>2.31</v>
       </c>
       <c r="U5" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="V5" t="n">
         <v>1.24</v>
       </c>
       <c r="W5" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="X5" t="n">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.53</v>
+        <v>1.48</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.45</v>
+        <v>2.6</v>
       </c>
       <c r="AA5" t="n">
         <v>2.45</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="AC5" t="n">
         <v>4.8</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="AF5" t="n">
-        <v>2.17</v>
+        <v>2</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AK5" t="n">
-        <v>1.31</v>
+        <v>1.44</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1319,7 +1319,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Macará</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,64 +1361,64 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>2.42</v>
+        <v>3.15</v>
       </c>
       <c r="O6" t="n">
-        <v>2.89</v>
+        <v>2.9</v>
       </c>
       <c r="P6" t="n">
-        <v>3.18</v>
+        <v>2.25</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.35</v>
+        <v>3.8</v>
       </c>
       <c r="R6" t="n">
-        <v>2.02</v>
+        <v>1.95</v>
       </c>
       <c r="S6" t="n">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="T6" t="n">
-        <v>2.31</v>
+        <v>2.28</v>
       </c>
       <c r="U6" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="V6" t="n">
         <v>1.24</v>
       </c>
       <c r="W6" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="X6" t="n">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.48</v>
+        <v>1.53</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.6</v>
+        <v>2.45</v>
       </c>
       <c r="AA6" t="n">
         <v>2.45</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="AC6" t="n">
         <v>4.8</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="AF6" t="n">
-        <v>2</v>
+        <v>2.17</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.44</v>
+        <v>1.31</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Curicó Unido</t>
+          <t>Deportes Santa Cruz</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Copiapó</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>2.63</v>
+        <v>2.12</v>
       </c>
       <c r="O7" t="n">
-        <v>3.35</v>
+        <v>3.15</v>
       </c>
       <c r="P7" t="n">
-        <v>2.3</v>
+        <v>3.1</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Barra do Garcas</t>
+          <t>Curicó Unido</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>2.15</v>
+        <v>2.63</v>
       </c>
       <c r="O8" t="n">
-        <v>2.89</v>
+        <v>3.35</v>
       </c>
       <c r="P8" t="n">
-        <v>3.6</v>
+        <v>2.3</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Deportes Santa Cruz</t>
+          <t>Barra do Garcas</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Copiapó</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,13 +1838,13 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>2.12</v>
+        <v>2.15</v>
       </c>
       <c r="O9" t="n">
-        <v>3.15</v>
+        <v>2.89</v>
       </c>
       <c r="P9" t="n">
-        <v>3.1</v>
+        <v>3.6</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>

--- a/jogos_2026-06-01.xlsx
+++ b/jogos_2026-06-01.xlsx
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Curicó Unido</t>
+          <t>Barra do Garcas</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>2.63</v>
+        <v>2.15</v>
       </c>
       <c r="O8" t="n">
-        <v>3.35</v>
+        <v>2.89</v>
       </c>
       <c r="P8" t="n">
-        <v>2.3</v>
+        <v>3.6</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Barra do Garcas</t>
+          <t>Curicó Unido</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,13 +1838,13 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>2.15</v>
+        <v>2.63</v>
       </c>
       <c r="O9" t="n">
-        <v>2.89</v>
+        <v>3.35</v>
       </c>
       <c r="P9" t="n">
-        <v>3.6</v>
+        <v>2.3</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>

--- a/jogos_2026-06-01.xlsx
+++ b/jogos_2026-06-01.xlsx
@@ -1214,7 +1214,7 @@
         <v>3.35</v>
       </c>
       <c r="R5" t="n">
-        <v>2.02</v>
+        <v>1.95</v>
       </c>
       <c r="S5" t="n">
         <v>1.56</v>
@@ -1238,28 +1238,28 @@
         <v>1.48</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.6</v>
+        <v>2.65</v>
       </c>
       <c r="AA5" t="n">
         <v>2.45</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AC5" t="n">
         <v>4.8</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AE5" t="n">
         <v>1.05</v>
       </c>
       <c r="AF5" t="n">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Deportes Santa Cruz</t>
+          <t>Curicó Unido</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Copiapó</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>2.12</v>
+        <v>2.63</v>
       </c>
       <c r="O7" t="n">
-        <v>3.15</v>
+        <v>3.35</v>
       </c>
       <c r="P7" t="n">
-        <v>3.1</v>
+        <v>2.3</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Curicó Unido</t>
+          <t>Deportes Santa Cruz</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Copiapó</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,13 +1838,13 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>2.63</v>
+        <v>2.12</v>
       </c>
       <c r="O9" t="n">
-        <v>3.35</v>
+        <v>3.15</v>
       </c>
       <c r="P9" t="n">
-        <v>2.3</v>
+        <v>3.1</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>

--- a/jogos_2026-06-01.xlsx
+++ b/jogos_2026-06-01.xlsx
@@ -1160,7 +1160,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Macará</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,64 +1202,64 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>2.42</v>
+        <v>3.15</v>
       </c>
       <c r="O5" t="n">
-        <v>2.89</v>
+        <v>2.9</v>
       </c>
       <c r="P5" t="n">
-        <v>3.18</v>
+        <v>2.25</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.35</v>
+        <v>3.8</v>
       </c>
       <c r="R5" t="n">
         <v>1.95</v>
       </c>
       <c r="S5" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="T5" t="n">
-        <v>2.31</v>
+        <v>2.28</v>
       </c>
       <c r="U5" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="V5" t="n">
         <v>1.24</v>
       </c>
       <c r="W5" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="X5" t="n">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.48</v>
+        <v>1.53</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.65</v>
+        <v>2.45</v>
       </c>
       <c r="AA5" t="n">
         <v>2.45</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.57</v>
+        <v>1.51</v>
       </c>
       <c r="AC5" t="n">
         <v>4.8</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.93</v>
+        <v>2.17</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AK5" t="n">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1319,7 +1319,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Macará</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,64 +1361,64 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>3.15</v>
+        <v>2.42</v>
       </c>
       <c r="O6" t="n">
-        <v>2.9</v>
+        <v>2.89</v>
       </c>
       <c r="P6" t="n">
-        <v>2.25</v>
+        <v>3.18</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.8</v>
+        <v>3.35</v>
       </c>
       <c r="R6" t="n">
         <v>1.95</v>
       </c>
       <c r="S6" t="n">
-        <v>1.5</v>
+        <v>1.56</v>
       </c>
       <c r="T6" t="n">
-        <v>2.28</v>
+        <v>2.31</v>
       </c>
       <c r="U6" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="V6" t="n">
         <v>1.24</v>
       </c>
       <c r="W6" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="X6" t="n">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.53</v>
+        <v>1.48</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.45</v>
+        <v>2.65</v>
       </c>
       <c r="AA6" t="n">
         <v>2.45</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.51</v>
+        <v>1.57</v>
       </c>
       <c r="AC6" t="n">
         <v>4.8</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="AF6" t="n">
-        <v>2.17</v>
+        <v>1.93</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.31</v>
+        <v>1.44</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Curicó Unido</t>
+          <t>Deportes Santa Cruz</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Copiapó</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,25 +1520,25 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>2.63</v>
+        <v>2.12</v>
       </c>
       <c r="O7" t="n">
-        <v>3.35</v>
+        <v>3.15</v>
       </c>
       <c r="P7" t="n">
-        <v>2.3</v>
+        <v>3.1</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="U7" t="n">
         <v>0</v>
@@ -1553,31 +1553,31 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK7" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Barra do Garcas</t>
+          <t>Curicó Unido</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,19 +1679,19 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>2.15</v>
+        <v>2.63</v>
       </c>
       <c r="O8" t="n">
-        <v>2.89</v>
+        <v>3.35</v>
       </c>
       <c r="P8" t="n">
-        <v>3.6</v>
+        <v>2.3</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
@@ -1700,10 +1700,10 @@
         <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
@@ -1712,31 +1712,31 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK8" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Deportes Santa Cruz</t>
+          <t>Barra do Garcas</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Copiapó</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,13 +1838,13 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>2.12</v>
+        <v>2.17</v>
       </c>
       <c r="O9" t="n">
-        <v>3.15</v>
+        <v>2.83</v>
       </c>
       <c r="P9" t="n">
-        <v>3.1</v>
+        <v>3.5</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
@@ -2006,55 +2006,55 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AK10" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2174,7 +2174,7 @@
         <v>1.5</v>
       </c>
       <c r="T11" t="n">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="U11" t="n">
         <v>3.4</v>

--- a/jogos_2026-06-01.xlsx
+++ b/jogos_2026-06-01.xlsx
@@ -1160,7 +1160,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Macará</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,64 +1202,64 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>3.15</v>
+        <v>2.42</v>
       </c>
       <c r="O5" t="n">
-        <v>2.9</v>
+        <v>2.89</v>
       </c>
       <c r="P5" t="n">
-        <v>2.25</v>
+        <v>3.18</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.8</v>
+        <v>3.35</v>
       </c>
       <c r="R5" t="n">
         <v>1.95</v>
       </c>
       <c r="S5" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="T5" t="n">
-        <v>2.28</v>
+        <v>2.31</v>
       </c>
       <c r="U5" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="V5" t="n">
         <v>1.24</v>
       </c>
       <c r="W5" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="X5" t="n">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.53</v>
+        <v>1.48</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.45</v>
+        <v>2.65</v>
       </c>
       <c r="AA5" t="n">
         <v>2.45</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.51</v>
+        <v>1.57</v>
       </c>
       <c r="AC5" t="n">
         <v>4.8</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="AF5" t="n">
-        <v>2.17</v>
+        <v>1.93</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AK5" t="n">
-        <v>1.3</v>
+        <v>1.44</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1319,7 +1319,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Macará</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,64 +1361,64 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>2.42</v>
+        <v>3.15</v>
       </c>
       <c r="O6" t="n">
-        <v>2.89</v>
+        <v>2.9</v>
       </c>
       <c r="P6" t="n">
-        <v>3.18</v>
+        <v>2.25</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.35</v>
+        <v>3.8</v>
       </c>
       <c r="R6" t="n">
         <v>1.95</v>
       </c>
       <c r="S6" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="T6" t="n">
-        <v>2.31</v>
+        <v>2.28</v>
       </c>
       <c r="U6" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="V6" t="n">
         <v>1.24</v>
       </c>
       <c r="W6" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="X6" t="n">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.48</v>
+        <v>1.53</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.65</v>
+        <v>2.45</v>
       </c>
       <c r="AA6" t="n">
         <v>2.45</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.57</v>
+        <v>1.51</v>
       </c>
       <c r="AC6" t="n">
         <v>4.8</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.93</v>
+        <v>2.17</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Deportes Santa Cruz</t>
+          <t>Curicó Unido</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Copiapó</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,80 +1520,80 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>2.12</v>
+        <v>2.63</v>
       </c>
       <c r="O7" t="n">
-        <v>3.15</v>
+        <v>3.35</v>
       </c>
       <c r="P7" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Q7" t="n">
         <v>3.1</v>
       </c>
-      <c r="Q7" t="n">
-        <v>2.7</v>
-      </c>
       <c r="R7" t="n">
-        <v>2.17</v>
+        <v>2.28</v>
       </c>
       <c r="S7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T7" t="n">
+        <v>0</v>
+      </c>
+      <c r="U7" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="V7" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="W7" t="n">
+        <v>0</v>
+      </c>
+      <c r="X7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ7" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AK7" t="n">
         <v>1.35</v>
-      </c>
-      <c r="T7" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="U7" t="n">
-        <v>0</v>
-      </c>
-      <c r="V7" t="n">
-        <v>0</v>
-      </c>
-      <c r="W7" t="n">
-        <v>0</v>
-      </c>
-      <c r="X7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ7" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>1.54</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Curicó Unido</t>
+          <t>Deportes Santa Cruz</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Copiapó</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,31 +1679,31 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>2.63</v>
+        <v>2.12</v>
       </c>
       <c r="O8" t="n">
-        <v>3.35</v>
+        <v>3.15</v>
       </c>
       <c r="P8" t="n">
-        <v>2.3</v>
+        <v>3.1</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.1</v>
+        <v>2.7</v>
       </c>
       <c r="R8" t="n">
-        <v>2.28</v>
+        <v>2.17</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="U8" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
@@ -1712,31 +1712,31 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.18</v>
+        <v>1.28</v>
       </c>
       <c r="Z8" t="n">
-        <v>4</v>
+        <v>3.15</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.61</v>
+        <v>1.9</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.08</v>
+        <v>1.75</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.5</v>
+        <v>3.25</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.43</v>
+        <v>1.26</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.15</v>
+        <v>1.08</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.52</v>
+        <v>1.72</v>
       </c>
       <c r="AG8" t="n">
-        <v>2.33</v>
+        <v>1.97</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.35</v>
+        <v>1.54</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -2006,55 +2006,55 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AG10" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AK10" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>

--- a/jogos_2026-06-01.xlsx
+++ b/jogos_2026-06-01.xlsx
@@ -1160,7 +1160,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Macará</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,64 +1202,64 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>2.42</v>
+        <v>3.15</v>
       </c>
       <c r="O5" t="n">
-        <v>2.89</v>
+        <v>2.9</v>
       </c>
       <c r="P5" t="n">
-        <v>3.18</v>
+        <v>2.25</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.35</v>
+        <v>3.8</v>
       </c>
       <c r="R5" t="n">
         <v>1.95</v>
       </c>
       <c r="S5" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="T5" t="n">
-        <v>2.31</v>
+        <v>2.28</v>
       </c>
       <c r="U5" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="V5" t="n">
         <v>1.24</v>
       </c>
       <c r="W5" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="X5" t="n">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.48</v>
+        <v>1.53</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.65</v>
+        <v>2.45</v>
       </c>
       <c r="AA5" t="n">
         <v>2.45</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.57</v>
+        <v>1.51</v>
       </c>
       <c r="AC5" t="n">
         <v>4.8</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.93</v>
+        <v>2.17</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AK5" t="n">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1319,7 +1319,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Macará</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,64 +1361,64 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>3.15</v>
+        <v>2.42</v>
       </c>
       <c r="O6" t="n">
-        <v>2.9</v>
+        <v>2.89</v>
       </c>
       <c r="P6" t="n">
-        <v>2.25</v>
+        <v>3.18</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.8</v>
+        <v>3.35</v>
       </c>
       <c r="R6" t="n">
         <v>1.95</v>
       </c>
       <c r="S6" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="T6" t="n">
-        <v>2.28</v>
+        <v>2.31</v>
       </c>
       <c r="U6" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="V6" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="W6" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="X6" t="n">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.53</v>
+        <v>1.48</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.45</v>
+        <v>2.65</v>
       </c>
       <c r="AA6" t="n">
         <v>2.45</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.51</v>
+        <v>1.57</v>
       </c>
       <c r="AC6" t="n">
         <v>4.8</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="AF6" t="n">
-        <v>2.17</v>
+        <v>1.93</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.3</v>
+        <v>1.44</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Curicó Unido</t>
+          <t>Barra do Garcas</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,19 +1520,19 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>2.63</v>
+        <v>2.17</v>
       </c>
       <c r="O7" t="n">
-        <v>3.35</v>
+        <v>2.83</v>
       </c>
       <c r="P7" t="n">
-        <v>2.3</v>
+        <v>3.5</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
@@ -1541,10 +1541,10 @@
         <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
@@ -1553,31 +1553,31 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AG7" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Barra do Garcas</t>
+          <t>Curicó Unido</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,19 +1838,19 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>2.17</v>
+        <v>2.63</v>
       </c>
       <c r="O9" t="n">
-        <v>2.83</v>
+        <v>3.35</v>
       </c>
       <c r="P9" t="n">
-        <v>3.5</v>
+        <v>2.3</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
@@ -1859,10 +1859,10 @@
         <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
@@ -1871,31 +1871,31 @@
         <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK9" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>

--- a/jogos_2026-06-01.xlsx
+++ b/jogos_2026-06-01.xlsx
@@ -1160,7 +1160,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Macará</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,64 +1202,64 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>3.15</v>
+        <v>2.42</v>
       </c>
       <c r="O5" t="n">
-        <v>2.9</v>
+        <v>2.89</v>
       </c>
       <c r="P5" t="n">
-        <v>2.25</v>
+        <v>3.18</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.8</v>
+        <v>3.35</v>
       </c>
       <c r="R5" t="n">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="S5" t="n">
         <v>1.55</v>
       </c>
       <c r="T5" t="n">
-        <v>2.28</v>
+        <v>2.25</v>
       </c>
       <c r="U5" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="V5" t="n">
         <v>1.24</v>
       </c>
       <c r="W5" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X5" t="n">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.53</v>
+        <v>1.48</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.45</v>
+        <v>2.65</v>
       </c>
       <c r="AA5" t="n">
         <v>2.45</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.51</v>
+        <v>1.57</v>
       </c>
       <c r="AC5" t="n">
         <v>4.8</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="AF5" t="n">
-        <v>2.17</v>
+        <v>1.93</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AK5" t="n">
-        <v>1.3</v>
+        <v>1.44</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1319,7 +1319,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Macará</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,64 +1361,64 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>2.42</v>
+        <v>3.15</v>
       </c>
       <c r="O6" t="n">
-        <v>2.89</v>
+        <v>2.9</v>
       </c>
       <c r="P6" t="n">
-        <v>3.18</v>
+        <v>2.25</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.35</v>
+        <v>3.7</v>
       </c>
       <c r="R6" t="n">
         <v>1.95</v>
       </c>
       <c r="S6" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="T6" t="n">
-        <v>2.31</v>
+        <v>2.28</v>
       </c>
       <c r="U6" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="V6" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="W6" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="X6" t="n">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.48</v>
+        <v>1.53</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.65</v>
+        <v>2.59</v>
       </c>
       <c r="AA6" t="n">
         <v>2.45</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.57</v>
+        <v>1.51</v>
       </c>
       <c r="AC6" t="n">
         <v>4.8</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="AE6" t="n">
         <v>1.05</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.93</v>
+        <v>2.17</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -2174,7 +2174,7 @@
         <v>1.5</v>
       </c>
       <c r="T11" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="U11" t="n">
         <v>3.4</v>

--- a/jogos_2026-06-01.xlsx
+++ b/jogos_2026-06-01.xlsx
@@ -1160,7 +1160,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Macará</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,64 +1202,64 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>2.42</v>
+        <v>3.15</v>
       </c>
       <c r="O5" t="n">
-        <v>2.89</v>
+        <v>2.9</v>
       </c>
       <c r="P5" t="n">
-        <v>3.18</v>
+        <v>2.25</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.35</v>
+        <v>3.7</v>
       </c>
       <c r="R5" t="n">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="S5" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="T5" t="n">
-        <v>2.25</v>
+        <v>2.28</v>
       </c>
       <c r="U5" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="V5" t="n">
         <v>1.24</v>
       </c>
       <c r="W5" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="X5" t="n">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.65</v>
+        <v>2.49</v>
       </c>
       <c r="AA5" t="n">
         <v>2.45</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AC5" t="n">
         <v>4.8</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AE5" t="n">
         <v>1.05</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.93</v>
+        <v>2.17</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AK5" t="n">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1319,7 +1319,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Macará</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,64 +1361,64 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>3.15</v>
+        <v>2.42</v>
       </c>
       <c r="O6" t="n">
-        <v>2.9</v>
+        <v>2.89</v>
       </c>
       <c r="P6" t="n">
-        <v>2.25</v>
+        <v>3.18</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.7</v>
+        <v>3.35</v>
       </c>
       <c r="R6" t="n">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="S6" t="n">
         <v>1.55</v>
       </c>
       <c r="T6" t="n">
-        <v>2.28</v>
+        <v>2.25</v>
       </c>
       <c r="U6" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="V6" t="n">
         <v>1.24</v>
       </c>
       <c r="W6" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X6" t="n">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.53</v>
+        <v>1.48</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.59</v>
+        <v>2.65</v>
       </c>
       <c r="AA6" t="n">
         <v>2.45</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.51</v>
+        <v>1.57</v>
       </c>
       <c r="AC6" t="n">
         <v>4.8</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="AE6" t="n">
         <v>1.05</v>
       </c>
       <c r="AF6" t="n">
-        <v>2.17</v>
+        <v>1.93</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.3</v>
+        <v>1.44</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Barra do Garcas</t>
+          <t>Curicó Unido</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,19 +1520,19 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>2.17</v>
+        <v>2.63</v>
       </c>
       <c r="O7" t="n">
-        <v>2.83</v>
+        <v>3.35</v>
       </c>
       <c r="P7" t="n">
-        <v>3.5</v>
+        <v>2.3</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
@@ -1541,10 +1541,10 @@
         <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
@@ -1553,31 +1553,31 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK7" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Curicó Unido</t>
+          <t>Barra do Garcas</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,19 +1838,19 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>2.63</v>
+        <v>2.1</v>
       </c>
       <c r="O9" t="n">
-        <v>3.35</v>
+        <v>2.87</v>
       </c>
       <c r="P9" t="n">
-        <v>2.3</v>
+        <v>3.5</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
@@ -1859,10 +1859,10 @@
         <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
@@ -1871,31 +1871,31 @@
         <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AG9" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -2006,55 +2006,55 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK10" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2156,13 +2156,13 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>2.95</v>
+        <v>2.93</v>
       </c>
       <c r="O11" t="n">
-        <v>2.9</v>
+        <v>2.98</v>
       </c>
       <c r="P11" t="n">
-        <v>2.3</v>
+        <v>2.45</v>
       </c>
       <c r="Q11" t="n">
         <v>3.45</v>
@@ -2174,7 +2174,7 @@
         <v>1.5</v>
       </c>
       <c r="T11" t="n">
-        <v>2.26</v>
+        <v>2.4</v>
       </c>
       <c r="U11" t="n">
         <v>3.4</v>
@@ -2186,19 +2186,19 @@
         <v>1.02</v>
       </c>
       <c r="X11" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="Y11" t="n">
         <v>1.4</v>
       </c>
       <c r="Z11" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="AA11" t="n">
         <v>2.49</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="AC11" t="n">
         <v>4.8</v>

--- a/jogos_2026-06-01.xlsx
+++ b/jogos_2026-06-01.xlsx
@@ -1160,7 +1160,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Macará</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,64 +1202,64 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>3.15</v>
+        <v>2.42</v>
       </c>
       <c r="O5" t="n">
-        <v>2.9</v>
+        <v>2.89</v>
       </c>
       <c r="P5" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="S5" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="T5" t="n">
         <v>2.25</v>
       </c>
-      <c r="Q5" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="R5" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="S5" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="T5" t="n">
-        <v>2.28</v>
-      </c>
       <c r="U5" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="V5" t="n">
         <v>1.24</v>
       </c>
       <c r="W5" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X5" t="n">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.49</v>
+        <v>2.65</v>
       </c>
       <c r="AA5" t="n">
         <v>2.45</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AC5" t="n">
         <v>4.8</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AE5" t="n">
         <v>1.05</v>
       </c>
       <c r="AF5" t="n">
-        <v>2.17</v>
+        <v>1.93</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AK5" t="n">
-        <v>1.3</v>
+        <v>1.44</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1319,7 +1319,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Macará</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,64 +1361,64 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>2.42</v>
+        <v>3.15</v>
       </c>
       <c r="O6" t="n">
-        <v>2.89</v>
+        <v>2.9</v>
       </c>
       <c r="P6" t="n">
-        <v>3.18</v>
+        <v>2.25</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.35</v>
+        <v>3.7</v>
       </c>
       <c r="R6" t="n">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="S6" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="T6" t="n">
-        <v>2.25</v>
+        <v>2.28</v>
       </c>
       <c r="U6" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="V6" t="n">
         <v>1.24</v>
       </c>
       <c r="W6" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="X6" t="n">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.65</v>
+        <v>2.49</v>
       </c>
       <c r="AA6" t="n">
         <v>2.45</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AC6" t="n">
         <v>4.8</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AE6" t="n">
         <v>1.05</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.93</v>
+        <v>2.17</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Curicó Unido</t>
+          <t>Barra do Garcas</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,19 +1520,19 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>2.63</v>
+        <v>2.1</v>
       </c>
       <c r="O7" t="n">
-        <v>3.35</v>
+        <v>2.87</v>
       </c>
       <c r="P7" t="n">
-        <v>2.3</v>
+        <v>3.5</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
@@ -1541,10 +1541,10 @@
         <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
@@ -1553,31 +1553,31 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AG7" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Deportes Santa Cruz</t>
+          <t>Curicó Unido</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Copiapó</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,80 +1679,80 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>2.12</v>
+        <v>2.63</v>
       </c>
       <c r="O8" t="n">
-        <v>3.15</v>
+        <v>3.35</v>
       </c>
       <c r="P8" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Q8" t="n">
         <v>3.1</v>
       </c>
-      <c r="Q8" t="n">
-        <v>2.7</v>
-      </c>
       <c r="R8" t="n">
-        <v>2.17</v>
+        <v>2.28</v>
       </c>
       <c r="S8" t="n">
+        <v>0</v>
+      </c>
+      <c r="T8" t="n">
+        <v>0</v>
+      </c>
+      <c r="U8" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="V8" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="W8" t="n">
+        <v>0</v>
+      </c>
+      <c r="X8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ8" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AK8" t="n">
         <v>1.35</v>
-      </c>
-      <c r="T8" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="U8" t="n">
-        <v>0</v>
-      </c>
-      <c r="V8" t="n">
-        <v>0</v>
-      </c>
-      <c r="W8" t="n">
-        <v>0</v>
-      </c>
-      <c r="X8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ8" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>1.54</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Barra do Garcas</t>
+          <t>Deportes Santa Cruz</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Copiapó</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,25 +1838,25 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="O9" t="n">
-        <v>2.87</v>
+        <v>3.15</v>
       </c>
       <c r="P9" t="n">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="U9" t="n">
         <v>0</v>
@@ -1871,31 +1871,31 @@
         <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK9" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -2006,55 +2006,55 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="AG10" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AK10" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>

--- a/jogos_2026-06-01.xlsx
+++ b/jogos_2026-06-01.xlsx
@@ -1253,7 +1253,7 @@
         <v>1.2</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="AF5" t="n">
         <v>1.93</v>
@@ -1394,22 +1394,22 @@
         <v>1.1</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.47</v>
+        <v>1.54</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.49</v>
+        <v>2.28</v>
       </c>
       <c r="AA6" t="n">
         <v>2.45</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="AC6" t="n">
         <v>4.8</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="AE6" t="n">
         <v>1.05</v>
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Barra do Garcas</t>
+          <t>Curicó Unido</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,19 +1520,19 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>2.1</v>
+        <v>2.63</v>
       </c>
       <c r="O7" t="n">
-        <v>2.87</v>
+        <v>3.35</v>
       </c>
       <c r="P7" t="n">
-        <v>3.5</v>
+        <v>2.3</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
@@ -1541,10 +1541,10 @@
         <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
@@ -1553,31 +1553,31 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK7" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Curicó Unido</t>
+          <t>Barra do Garcas</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,19 +1679,19 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>2.63</v>
+        <v>2.1</v>
       </c>
       <c r="O8" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="P8" t="n">
         <v>3.35</v>
       </c>
-      <c r="P8" t="n">
-        <v>2.3</v>
-      </c>
       <c r="Q8" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
@@ -1700,10 +1700,10 @@
         <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
@@ -1712,31 +1712,31 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AG8" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1908,7 +1908,7 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AK9" t="n">
         <v>1.54</v>
@@ -2006,55 +2006,55 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK10" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2159,10 +2159,10 @@
         <v>2.93</v>
       </c>
       <c r="O11" t="n">
-        <v>2.98</v>
+        <v>2.9</v>
       </c>
       <c r="P11" t="n">
-        <v>2.45</v>
+        <v>2.3</v>
       </c>
       <c r="Q11" t="n">
         <v>3.45</v>
@@ -2192,13 +2192,13 @@
         <v>1.4</v>
       </c>
       <c r="Z11" t="n">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="AA11" t="n">
         <v>2.49</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="AC11" t="n">
         <v>4.8</v>

--- a/jogos_2026-06-01.xlsx
+++ b/jogos_2026-06-01.xlsx
@@ -1217,10 +1217,10 @@
         <v>1.9</v>
       </c>
       <c r="S5" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="T5" t="n">
-        <v>2.25</v>
+        <v>2.31</v>
       </c>
       <c r="U5" t="n">
         <v>3.3</v>
@@ -1229,7 +1229,7 @@
         <v>1.24</v>
       </c>
       <c r="W5" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="X5" t="n">
         <v>1.05</v>
@@ -1253,7 +1253,7 @@
         <v>1.2</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="AF5" t="n">
         <v>1.93</v>
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Curicó Unido</t>
+          <t>Barra do Garcas</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,19 +1520,19 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>2.63</v>
+        <v>2.16</v>
       </c>
       <c r="O7" t="n">
-        <v>3.35</v>
+        <v>2.75</v>
       </c>
       <c r="P7" t="n">
-        <v>2.3</v>
+        <v>3.34</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
@@ -1541,10 +1541,10 @@
         <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
@@ -1553,31 +1553,31 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AG7" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Barra do Garcas</t>
+          <t>Curicó Unido</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,19 +1679,19 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>2.1</v>
+        <v>2.63</v>
       </c>
       <c r="O8" t="n">
-        <v>2.87</v>
+        <v>3.35</v>
       </c>
       <c r="P8" t="n">
-        <v>3.35</v>
+        <v>2.3</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
@@ -1700,10 +1700,10 @@
         <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
@@ -1712,31 +1712,31 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK8" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>

--- a/jogos_2026-06-01.xlsx
+++ b/jogos_2026-06-01.xlsx
@@ -1211,7 +1211,7 @@
         <v>3.18</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="R5" t="n">
         <v>1.9</v>
@@ -1397,7 +1397,7 @@
         <v>1.54</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.28</v>
+        <v>2.45</v>
       </c>
       <c r="AA6" t="n">
         <v>2.45</v>
@@ -1409,10 +1409,10 @@
         <v>4.8</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="AF6" t="n">
         <v>2.17</v>
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Barra do Garcas</t>
+          <t>Deportes Santa Cruz</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Copiapó</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,25 +1520,25 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>2.16</v>
+        <v>2.12</v>
       </c>
       <c r="O7" t="n">
-        <v>2.75</v>
+        <v>3.15</v>
       </c>
       <c r="P7" t="n">
-        <v>3.34</v>
+        <v>3.1</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="U7" t="n">
         <v>0</v>
@@ -1553,31 +1553,31 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK7" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Deportes Santa Cruz</t>
+          <t>Barra do Garcas</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Copiapó</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,25 +1838,25 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="O9" t="n">
-        <v>3.15</v>
+        <v>2.8</v>
       </c>
       <c r="P9" t="n">
-        <v>3.1</v>
+        <v>3.56</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
         <v>0</v>
@@ -1871,31 +1871,31 @@
         <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1997,34 +1997,34 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="Q10" t="n">
         <v>2.75</v>
       </c>
       <c r="R10" t="n">
-        <v>2.3</v>
+        <v>2.12</v>
       </c>
       <c r="S10" t="n">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="T10" t="n">
-        <v>2.96</v>
+        <v>3.25</v>
       </c>
       <c r="U10" t="n">
         <v>2.36</v>
       </c>
       <c r="V10" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="W10" t="n">
-        <v>1.13</v>
+        <v>1.09</v>
       </c>
       <c r="X10" t="n">
         <v>1.01</v>
@@ -2033,19 +2033,19 @@
         <v>1.16</v>
       </c>
       <c r="Z10" t="n">
-        <v>4.1</v>
+        <v>4.05</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.25</v>
+        <v>2.14</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.42</v>
+        <v>2.43</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="AE10" t="n">
         <v>1.15</v>
@@ -2195,7 +2195,7 @@
         <v>2.4</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.49</v>
+        <v>2.55</v>
       </c>
       <c r="AB11" t="n">
         <v>1.47</v>

--- a/jogos_2026-06-01.xlsx
+++ b/jogos_2026-06-01.xlsx
@@ -1385,7 +1385,7 @@
         <v>3.4</v>
       </c>
       <c r="V6" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="W6" t="n">
         <v>1.01</v>
@@ -1403,7 +1403,7 @@
         <v>2.45</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.44</v>
+        <v>1.51</v>
       </c>
       <c r="AC6" t="n">
         <v>4.8</v>
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Deportes Santa Cruz</t>
+          <t>Barra do Garcas</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Copiapó</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,25 +1520,25 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="O7" t="n">
-        <v>3.15</v>
+        <v>2.8</v>
       </c>
       <c r="P7" t="n">
-        <v>3.1</v>
+        <v>3.56</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
         <v>0</v>
@@ -1553,31 +1553,31 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>2.63</v>
+        <v>2.6</v>
       </c>
       <c r="O8" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="P8" t="n">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="Q8" t="n">
         <v>3.1</v>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Barra do Garcas</t>
+          <t>Deportes Santa Cruz</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Copiapó</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,25 +1838,25 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="O9" t="n">
-        <v>2.8</v>
+        <v>3.1</v>
       </c>
       <c r="P9" t="n">
-        <v>3.56</v>
+        <v>3.05</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="U9" t="n">
         <v>0</v>
@@ -1871,31 +1871,31 @@
         <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK9" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>

--- a/jogos_2026-06-01.xlsx
+++ b/jogos_2026-06-01.xlsx
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Barra do Garcas</t>
+          <t>Curicó Unido</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,19 +1520,19 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>2.1</v>
+        <v>2.6</v>
       </c>
       <c r="O7" t="n">
-        <v>2.8</v>
+        <v>3.3</v>
       </c>
       <c r="P7" t="n">
-        <v>3.56</v>
+        <v>2.25</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
@@ -1541,10 +1541,10 @@
         <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
@@ -1553,31 +1553,31 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK7" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Curicó Unido</t>
+          <t>Deportes Santa Cruz</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Copiapó</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,31 +1679,31 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>2.6</v>
+        <v>2.11</v>
       </c>
       <c r="O8" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="P8" t="n">
-        <v>2.25</v>
+        <v>3.05</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.1</v>
+        <v>2.7</v>
       </c>
       <c r="R8" t="n">
-        <v>2.28</v>
+        <v>2.17</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="U8" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
@@ -1712,31 +1712,31 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.18</v>
+        <v>1.28</v>
       </c>
       <c r="Z8" t="n">
-        <v>4</v>
+        <v>3.15</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.61</v>
+        <v>1.9</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.08</v>
+        <v>1.75</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.5</v>
+        <v>3.25</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.43</v>
+        <v>1.26</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.15</v>
+        <v>1.08</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.52</v>
+        <v>1.72</v>
       </c>
       <c r="AG8" t="n">
-        <v>2.33</v>
+        <v>1.97</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.35</v>
+        <v>1.54</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Deportes Santa Cruz</t>
+          <t>Barra do Garcas</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Copiapó</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,25 +1838,25 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="O9" t="n">
-        <v>3.1</v>
+        <v>2.8</v>
       </c>
       <c r="P9" t="n">
-        <v>3.05</v>
+        <v>3.56</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
         <v>0</v>
@@ -1871,31 +1871,31 @@
         <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>

--- a/jogos_2026-06-01.xlsx
+++ b/jogos_2026-06-01.xlsx
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Curicó Unido</t>
+          <t>Barra do Garcas</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,19 +1520,19 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>2.6</v>
+        <v>2.1</v>
       </c>
       <c r="O7" t="n">
-        <v>3.3</v>
+        <v>2.8</v>
       </c>
       <c r="P7" t="n">
-        <v>2.25</v>
+        <v>3.56</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
@@ -1541,10 +1541,10 @@
         <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
@@ -1553,31 +1553,31 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AG7" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Deportes Santa Cruz</t>
+          <t>Curicó Unido</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Copiapó</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,80 +1679,80 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>2.11</v>
+        <v>2.6</v>
       </c>
       <c r="O8" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="P8" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Q8" t="n">
         <v>3.1</v>
       </c>
-      <c r="P8" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>2.7</v>
-      </c>
       <c r="R8" t="n">
-        <v>2.17</v>
+        <v>2.28</v>
       </c>
       <c r="S8" t="n">
+        <v>0</v>
+      </c>
+      <c r="T8" t="n">
+        <v>0</v>
+      </c>
+      <c r="U8" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="V8" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="W8" t="n">
+        <v>0</v>
+      </c>
+      <c r="X8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ8" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AK8" t="n">
         <v>1.35</v>
-      </c>
-      <c r="T8" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="U8" t="n">
-        <v>0</v>
-      </c>
-      <c r="V8" t="n">
-        <v>0</v>
-      </c>
-      <c r="W8" t="n">
-        <v>0</v>
-      </c>
-      <c r="X8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ8" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>1.54</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Barra do Garcas</t>
+          <t>Deportes Santa Cruz</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Copiapó</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,25 +1838,25 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="O9" t="n">
-        <v>2.8</v>
+        <v>3.1</v>
       </c>
       <c r="P9" t="n">
-        <v>3.56</v>
+        <v>3.05</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="U9" t="n">
         <v>0</v>
@@ -1871,31 +1871,31 @@
         <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK9" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>

--- a/jogos_2026-06-01.xlsx
+++ b/jogos_2026-06-01.xlsx
@@ -1160,7 +1160,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Macará</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,64 +1202,64 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>2.42</v>
+        <v>3.15</v>
       </c>
       <c r="O5" t="n">
-        <v>2.89</v>
+        <v>2.9</v>
       </c>
       <c r="P5" t="n">
-        <v>3.18</v>
+        <v>2.25</v>
       </c>
       <c r="Q5" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="S5" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="U5" t="n">
         <v>3.4</v>
       </c>
-      <c r="R5" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="S5" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="T5" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="U5" t="n">
-        <v>3.3</v>
-      </c>
       <c r="V5" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="W5" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="X5" t="n">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.48</v>
+        <v>1.54</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.65</v>
+        <v>2.45</v>
       </c>
       <c r="AA5" t="n">
         <v>2.45</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.57</v>
+        <v>1.51</v>
       </c>
       <c r="AC5" t="n">
         <v>4.8</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.93</v>
+        <v>2.17</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AK5" t="n">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1319,7 +1319,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Macará</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,64 +1361,64 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>3.15</v>
+        <v>2.42</v>
       </c>
       <c r="O6" t="n">
-        <v>2.9</v>
+        <v>2.89</v>
       </c>
       <c r="P6" t="n">
-        <v>2.25</v>
+        <v>3.18</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.7</v>
+        <v>3.4</v>
       </c>
       <c r="R6" t="n">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="S6" t="n">
-        <v>1.5</v>
+        <v>1.56</v>
       </c>
       <c r="T6" t="n">
-        <v>2.28</v>
+        <v>2.31</v>
       </c>
       <c r="U6" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="V6" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="W6" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="X6" t="n">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.54</v>
+        <v>1.48</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.45</v>
+        <v>2.65</v>
       </c>
       <c r="AA6" t="n">
         <v>2.45</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.51</v>
+        <v>1.57</v>
       </c>
       <c r="AC6" t="n">
         <v>4.8</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="AF6" t="n">
-        <v>2.17</v>
+        <v>1.93</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.3</v>
+        <v>1.44</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Curicó Unido</t>
+          <t>Deportes Santa Cruz</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Copiapó</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,31 +1679,31 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>2.6</v>
+        <v>2.11</v>
       </c>
       <c r="O8" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="P8" t="n">
-        <v>2.25</v>
+        <v>3.05</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.1</v>
+        <v>2.7</v>
       </c>
       <c r="R8" t="n">
-        <v>2.28</v>
+        <v>2.17</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="U8" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
@@ -1712,31 +1712,31 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.18</v>
+        <v>1.28</v>
       </c>
       <c r="Z8" t="n">
-        <v>4</v>
+        <v>3.15</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.61</v>
+        <v>1.9</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.08</v>
+        <v>1.75</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.5</v>
+        <v>3.25</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.43</v>
+        <v>1.26</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.15</v>
+        <v>1.08</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.52</v>
+        <v>1.72</v>
       </c>
       <c r="AG8" t="n">
-        <v>2.33</v>
+        <v>1.97</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.35</v>
+        <v>1.54</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Deportes Santa Cruz</t>
+          <t>Curicó Unido</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Copiapó</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,80 +1838,80 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>2.11</v>
+        <v>2.6</v>
       </c>
       <c r="O9" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="P9" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Q9" t="n">
         <v>3.1</v>
       </c>
-      <c r="P9" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>2.7</v>
-      </c>
       <c r="R9" t="n">
-        <v>2.17</v>
+        <v>2.28</v>
       </c>
       <c r="S9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U9" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="V9" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="W9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ9" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AK9" t="n">
         <v>1.35</v>
-      </c>
-      <c r="T9" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="U9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V9" t="n">
-        <v>0</v>
-      </c>
-      <c r="W9" t="n">
-        <v>0</v>
-      </c>
-      <c r="X9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ9" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AK9" t="n">
-        <v>1.54</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>

--- a/jogos_2026-06-01.xlsx
+++ b/jogos_2026-06-01.xlsx
@@ -734,55 +734,55 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -795,10 +795,10 @@
         </is>
       </c>
       <c r="AJ2" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AK2" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AL2" t="n">
         <v>0</v>
@@ -884,64 +884,64 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="O3" t="n">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="P3" t="n">
-        <v>2.65</v>
+        <v>2.5</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="AJ3" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AK3" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -1043,64 +1043,64 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>2.14</v>
+        <v>2</v>
       </c>
       <c r="O4" t="n">
         <v>2.95</v>
       </c>
       <c r="P4" t="n">
-        <v>3.3</v>
+        <v>3.56</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AK4" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1202,16 +1202,16 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>3.15</v>
+        <v>3.06</v>
       </c>
       <c r="O5" t="n">
         <v>2.9</v>
       </c>
       <c r="P5" t="n">
-        <v>2.25</v>
+        <v>2.27</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="R5" t="n">
         <v>1.95</v>
@@ -1220,13 +1220,13 @@
         <v>1.5</v>
       </c>
       <c r="T5" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="U5" t="n">
         <v>3.4</v>
       </c>
       <c r="V5" t="n">
-        <v>1.23</v>
+        <v>1.18</v>
       </c>
       <c r="W5" t="n">
         <v>1.01</v>
@@ -1244,7 +1244,7 @@
         <v>2.45</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.51</v>
+        <v>1.44</v>
       </c>
       <c r="AC5" t="n">
         <v>4.8</v>
@@ -1275,7 +1275,7 @@
         <v>1.36</v>
       </c>
       <c r="AK5" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1361,19 +1361,19 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>2.42</v>
+        <v>2.53</v>
       </c>
       <c r="O6" t="n">
-        <v>2.89</v>
+        <v>2.8</v>
       </c>
       <c r="P6" t="n">
-        <v>3.18</v>
+        <v>2.74</v>
       </c>
       <c r="Q6" t="n">
         <v>3.4</v>
       </c>
       <c r="R6" t="n">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="S6" t="n">
         <v>1.56</v>
@@ -1382,10 +1382,10 @@
         <v>2.31</v>
       </c>
       <c r="U6" t="n">
-        <v>3.3</v>
+        <v>3.7</v>
       </c>
       <c r="V6" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="W6" t="n">
         <v>1.04</v>
@@ -1431,7 +1431,7 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="AK6" t="n">
         <v>1.44</v>
@@ -1520,7 +1520,7 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="O7" t="n">
         <v>2.8</v>
@@ -1529,55 +1529,55 @@
         <v>3.56</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AK7" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1679,19 +1679,19 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>2.11</v>
+        <v>2.4</v>
       </c>
       <c r="O8" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="P8" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Q8" t="n">
         <v>3.1</v>
       </c>
-      <c r="P8" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>2.7</v>
-      </c>
       <c r="R8" t="n">
-        <v>2.17</v>
+        <v>2.06</v>
       </c>
       <c r="S8" t="n">
         <v>1.35</v>
@@ -1700,40 +1700,40 @@
         <v>2.7</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y8" t="n">
         <v>1.28</v>
       </c>
       <c r="Z8" t="n">
-        <v>3.15</v>
+        <v>3.08</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="AC8" t="n">
-        <v>3.25</v>
+        <v>3.28</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="AG8" t="n">
         <v>1.97</v>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.54</v>
+        <v>1.44</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1838,80 +1838,80 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>2.6</v>
+        <v>2.45</v>
       </c>
       <c r="O9" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="P9" t="n">
-        <v>2.25</v>
+        <v>2.5</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.1</v>
+        <v>3.06</v>
       </c>
       <c r="R9" t="n">
-        <v>2.28</v>
+        <v>2.1</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="U9" t="n">
-        <v>2.28</v>
+        <v>2.59</v>
       </c>
       <c r="V9" t="n">
-        <v>1.49</v>
+        <v>1.41</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="Z9" t="n">
-        <v>4</v>
+        <v>3.58</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.61</v>
+        <v>1.77</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.08</v>
+        <v>1.94</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.5</v>
+        <v>2.83</v>
       </c>
       <c r="AD9" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ9" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AK9" t="n">
         <v>1.43</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ9" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AK9" t="n">
-        <v>1.35</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1997,31 +1997,31 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>2.15</v>
+        <v>2.11</v>
       </c>
       <c r="O10" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="P10" t="n">
         <v>2.9</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="R10" t="n">
-        <v>2.12</v>
+        <v>2.3</v>
       </c>
       <c r="S10" t="n">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="T10" t="n">
-        <v>3.25</v>
+        <v>2.96</v>
       </c>
       <c r="U10" t="n">
-        <v>2.36</v>
+        <v>2.33</v>
       </c>
       <c r="V10" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="W10" t="n">
         <v>1.09</v>
@@ -2030,28 +2030,28 @@
         <v>1.01</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="Z10" t="n">
-        <v>4.05</v>
+        <v>4.1</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.43</v>
+        <v>2.39</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.48</v>
+        <v>1.45</v>
       </c>
       <c r="AE10" t="n">
         <v>1.15</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="AG10" t="n">
         <v>2.36</v>
@@ -2070,7 +2070,7 @@
         <v>1.25</v>
       </c>
       <c r="AK10" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2159,10 +2159,10 @@
         <v>2.93</v>
       </c>
       <c r="O11" t="n">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="P11" t="n">
-        <v>2.3</v>
+        <v>2.37</v>
       </c>
       <c r="Q11" t="n">
         <v>3.45</v>
@@ -2183,7 +2183,7 @@
         <v>1.22</v>
       </c>
       <c r="W11" t="n">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="X11" t="n">
         <v>1.06</v>

--- a/jogos_2026-06-01.xlsx
+++ b/jogos_2026-06-01.xlsx
@@ -737,10 +737,10 @@
         <v>3.22</v>
       </c>
       <c r="R2" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="S2" t="n">
-        <v>1.49</v>
+        <v>1.51</v>
       </c>
       <c r="T2" t="n">
         <v>2.36</v>
@@ -764,10 +764,10 @@
         <v>2.62</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.27</v>
+        <v>2.33</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="AC2" t="n">
         <v>4.25</v>
@@ -779,10 +779,10 @@
         <v>1.01</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         </is>
       </c>
       <c r="AJ2" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="AK2" t="n">
         <v>1.44</v>
@@ -887,10 +887,10 @@
         <v>2.75</v>
       </c>
       <c r="O3" t="n">
-        <v>2.75</v>
+        <v>2.72</v>
       </c>
       <c r="P3" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="Q3" t="n">
         <v>3.3</v>
@@ -902,7 +902,7 @@
         <v>1.62</v>
       </c>
       <c r="T3" t="n">
-        <v>2.4</v>
+        <v>2.15</v>
       </c>
       <c r="U3" t="n">
         <v>3.78</v>
@@ -914,25 +914,25 @@
         <v>1.01</v>
       </c>
       <c r="X3" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.52</v>
+        <v>1.57</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.55</v>
+        <v>2.33</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.6</v>
+        <v>2.84</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="AC3" t="n">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="AE3" t="n">
         <v>1.03</v>
@@ -941,7 +941,7 @@
         <v>2.15</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -957,7 +957,7 @@
         <v>1.35</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -1046,25 +1046,25 @@
         <v>2</v>
       </c>
       <c r="O4" t="n">
-        <v>2.95</v>
+        <v>2.85</v>
       </c>
       <c r="P4" t="n">
-        <v>3.56</v>
+        <v>3.75</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.83</v>
+        <v>2.64</v>
       </c>
       <c r="R4" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="S4" t="n">
-        <v>1.61</v>
+        <v>1.47</v>
       </c>
       <c r="T4" t="n">
-        <v>2.17</v>
+        <v>2.33</v>
       </c>
       <c r="U4" t="n">
-        <v>3.8</v>
+        <v>3.92</v>
       </c>
       <c r="V4" t="n">
         <v>1.18</v>
@@ -1076,25 +1076,25 @@
         <v>1.07</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.25</v>
+        <v>2.29</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.7</v>
+        <v>2.85</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="AC4" t="n">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AF4" t="n">
         <v>2.2</v>
@@ -1160,7 +1160,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Macará</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,64 +1202,64 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>3.06</v>
+        <v>2.45</v>
       </c>
       <c r="O5" t="n">
         <v>2.9</v>
       </c>
       <c r="P5" t="n">
-        <v>2.27</v>
+        <v>2.6</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.65</v>
+        <v>3.45</v>
       </c>
       <c r="R5" t="n">
-        <v>1.95</v>
+        <v>1.82</v>
       </c>
       <c r="S5" t="n">
-        <v>1.5</v>
+        <v>1.56</v>
       </c>
       <c r="T5" t="n">
-        <v>2.26</v>
+        <v>2.31</v>
       </c>
       <c r="U5" t="n">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
       <c r="V5" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="W5" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="X5" t="n">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.54</v>
+        <v>1.45</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.45</v>
+        <v>2.7</v>
       </c>
       <c r="AA5" t="n">
         <v>2.45</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.44</v>
+        <v>1.57</v>
       </c>
       <c r="AC5" t="n">
         <v>4.8</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="AF5" t="n">
-        <v>2.17</v>
+        <v>1.91</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="AK5" t="n">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1319,7 +1319,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Macará</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,64 +1361,64 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>2.53</v>
+        <v>3.06</v>
       </c>
       <c r="O6" t="n">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="P6" t="n">
-        <v>2.74</v>
+        <v>2.4</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.4</v>
+        <v>3.65</v>
       </c>
       <c r="R6" t="n">
         <v>1.95</v>
       </c>
       <c r="S6" t="n">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="T6" t="n">
-        <v>2.31</v>
+        <v>2.26</v>
       </c>
       <c r="U6" t="n">
-        <v>3.7</v>
+        <v>3.4</v>
       </c>
       <c r="V6" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="W6" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="X6" t="n">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.48</v>
+        <v>1.54</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.65</v>
+        <v>2.45</v>
       </c>
       <c r="AA6" t="n">
         <v>2.45</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.57</v>
+        <v>1.44</v>
       </c>
       <c r="AC6" t="n">
         <v>4.8</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.93</v>
+        <v>2.17</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.44</v>
+        <v>1.33</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Barra do Garcas</t>
+          <t>Curicó Unido</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,80 +1520,80 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>2.12</v>
+        <v>2.45</v>
       </c>
       <c r="O7" t="n">
-        <v>2.8</v>
+        <v>3.25</v>
       </c>
       <c r="P7" t="n">
-        <v>3.56</v>
+        <v>2.45</v>
       </c>
       <c r="Q7" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="R7" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="S7" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="T7" t="n">
         <v>2.9</v>
       </c>
-      <c r="R7" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="S7" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="T7" t="n">
-        <v>2.28</v>
-      </c>
       <c r="U7" t="n">
-        <v>3.5</v>
+        <v>2.65</v>
       </c>
       <c r="V7" t="n">
-        <v>1.22</v>
+        <v>1.43</v>
       </c>
       <c r="W7" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X7" t="n">
         <v>1.01</v>
       </c>
-      <c r="X7" t="n">
-        <v>1.05</v>
-      </c>
       <c r="Y7" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ7" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AK7" t="n">
         <v>1.43</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ7" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>1.62</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Deportes Santa Cruz</t>
+          <t>Barra do Garcas</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Copiapó</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,64 +1679,64 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>2.4</v>
+        <v>2.12</v>
       </c>
       <c r="O8" t="n">
-        <v>3.2</v>
+        <v>2.8</v>
       </c>
       <c r="P8" t="n">
-        <v>2.5</v>
+        <v>3.56</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="R8" t="n">
-        <v>2.06</v>
+        <v>1.95</v>
       </c>
       <c r="S8" t="n">
-        <v>1.35</v>
+        <v>1.54</v>
       </c>
       <c r="T8" t="n">
-        <v>2.7</v>
+        <v>2.28</v>
       </c>
       <c r="U8" t="n">
-        <v>2.82</v>
+        <v>3.5</v>
       </c>
       <c r="V8" t="n">
-        <v>1.35</v>
+        <v>1.22</v>
       </c>
       <c r="W8" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="X8" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AE8" t="n">
         <v>1.01</v>
       </c>
-      <c r="Y8" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>1.06</v>
-      </c>
       <c r="AF8" t="n">
-        <v>1.73</v>
+        <v>2.04</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.97</v>
+        <v>1.66</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.26</v>
+        <v>1.31</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.44</v>
+        <v>1.62</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Curicó Unido</t>
+          <t>Deportes Santa Cruz</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Copiapó</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,64 +1838,64 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>2.45</v>
+        <v>2.15</v>
       </c>
       <c r="O9" t="n">
         <v>3.2</v>
       </c>
       <c r="P9" t="n">
-        <v>2.5</v>
+        <v>2.62</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.06</v>
+        <v>2.81</v>
       </c>
       <c r="R9" t="n">
-        <v>2.1</v>
+        <v>2.07</v>
       </c>
       <c r="S9" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="T9" t="n">
-        <v>2.9</v>
+        <v>2.7</v>
       </c>
       <c r="U9" t="n">
-        <v>2.59</v>
+        <v>2.8</v>
       </c>
       <c r="V9" t="n">
-        <v>1.41</v>
+        <v>1.36</v>
       </c>
       <c r="W9" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AE9" t="n">
         <v>1.06</v>
       </c>
-      <c r="X9" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>3.58</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>1.09</v>
-      </c>
       <c r="AF9" t="n">
-        <v>1.65</v>
+        <v>1.73</v>
       </c>
       <c r="AG9" t="n">
-        <v>2.16</v>
+        <v>1.98</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1911,7 +1911,7 @@
         <v>1.25</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1997,13 +1997,13 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="O10" t="n">
         <v>3.4</v>
       </c>
       <c r="P10" t="n">
-        <v>2.9</v>
+        <v>2.85</v>
       </c>
       <c r="Q10" t="n">
         <v>2.8</v>
@@ -2027,10 +2027,10 @@
         <v>1.09</v>
       </c>
       <c r="X10" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="Z10" t="n">
         <v>4.1</v>
@@ -2039,10 +2039,10 @@
         <v>1.62</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.39</v>
+        <v>2.63</v>
       </c>
       <c r="AD10" t="n">
         <v>1.45</v>
@@ -2156,13 +2156,13 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>2.93</v>
+        <v>2.91</v>
       </c>
       <c r="O11" t="n">
-        <v>2.8</v>
+        <v>2.87</v>
       </c>
       <c r="P11" t="n">
-        <v>2.37</v>
+        <v>2.17</v>
       </c>
       <c r="Q11" t="n">
         <v>3.45</v>
@@ -2174,7 +2174,7 @@
         <v>1.5</v>
       </c>
       <c r="T11" t="n">
-        <v>2.4</v>
+        <v>1.98</v>
       </c>
       <c r="U11" t="n">
         <v>3.4</v>
@@ -2183,7 +2183,7 @@
         <v>1.22</v>
       </c>
       <c r="W11" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="X11" t="n">
         <v>1.06</v>
@@ -2195,10 +2195,10 @@
         <v>2.4</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.55</v>
+        <v>2.49</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="AC11" t="n">
         <v>4.8</v>
@@ -2229,7 +2229,7 @@
         <v>1.36</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>

--- a/jogos_2026-06-01.xlsx
+++ b/jogos_2026-06-01.xlsx
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Curicó Unido</t>
+          <t>Barra do Garcas</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,64 +1520,64 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>2.45</v>
+        <v>2.03</v>
       </c>
       <c r="O7" t="n">
-        <v>3.25</v>
+        <v>2.85</v>
       </c>
       <c r="P7" t="n">
-        <v>2.45</v>
+        <v>3.72</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.06</v>
+        <v>2.82</v>
       </c>
       <c r="R7" t="n">
-        <v>2.1</v>
+        <v>1.82</v>
       </c>
       <c r="S7" t="n">
-        <v>1.33</v>
+        <v>1.54</v>
       </c>
       <c r="T7" t="n">
-        <v>2.9</v>
+        <v>2.28</v>
       </c>
       <c r="U7" t="n">
-        <v>2.65</v>
+        <v>3.5</v>
       </c>
       <c r="V7" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="W7" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X7" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y7" t="n">
         <v>1.43</v>
       </c>
-      <c r="W7" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="X7" t="n">
+      <c r="Z7" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AE7" t="n">
         <v>1.01</v>
       </c>
-      <c r="Y7" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>3.58</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>1.09</v>
-      </c>
       <c r="AF7" t="n">
-        <v>1.65</v>
+        <v>2.04</v>
       </c>
       <c r="AG7" t="n">
-        <v>2.16</v>
+        <v>1.66</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.43</v>
+        <v>1.62</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Barra do Garcas</t>
+          <t>Deportes Santa Cruz</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Copiapó</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,64 +1679,64 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>2.12</v>
+        <v>2.15</v>
       </c>
       <c r="O8" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="P8" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="R8" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="S8" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="U8" t="n">
         <v>2.8</v>
       </c>
-      <c r="P8" t="n">
-        <v>3.56</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="R8" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="S8" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="T8" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="U8" t="n">
-        <v>3.5</v>
-      </c>
       <c r="V8" t="n">
-        <v>1.22</v>
+        <v>1.36</v>
       </c>
       <c r="W8" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="X8" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.43</v>
+        <v>1.27</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.46</v>
+        <v>3.14</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.47</v>
+        <v>1.93</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.5</v>
+        <v>1.78</v>
       </c>
       <c r="AC8" t="n">
-        <v>4.7</v>
+        <v>3.4</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.12</v>
+        <v>1.29</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="AF8" t="n">
-        <v>2.04</v>
+        <v>1.73</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.66</v>
+        <v>1.98</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.31</v>
+        <v>1.25</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.62</v>
+        <v>1.53</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Deportes Santa Cruz</t>
+          <t>Curicó Unido</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Copiapó</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,64 +1838,64 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>2.15</v>
+        <v>2.45</v>
       </c>
       <c r="O9" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="P9" t="n">
-        <v>2.62</v>
+        <v>2.45</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.81</v>
+        <v>3.06</v>
       </c>
       <c r="R9" t="n">
-        <v>2.07</v>
+        <v>2.1</v>
       </c>
       <c r="S9" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="T9" t="n">
-        <v>2.7</v>
+        <v>2.9</v>
       </c>
       <c r="U9" t="n">
-        <v>2.8</v>
+        <v>2.65</v>
       </c>
       <c r="V9" t="n">
-        <v>1.36</v>
+        <v>1.43</v>
       </c>
       <c r="W9" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X9" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.27</v>
+        <v>1.21</v>
       </c>
       <c r="Z9" t="n">
-        <v>3.14</v>
+        <v>3.58</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.93</v>
+        <v>1.77</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.78</v>
+        <v>1.94</v>
       </c>
       <c r="AC9" t="n">
-        <v>3.4</v>
+        <v>2.83</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.73</v>
+        <v>1.65</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.98</v>
+        <v>2.16</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1911,7 +1911,7 @@
         <v>1.25</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.53</v>
+        <v>1.43</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>

--- a/jogos_2026-06-01.xlsx
+++ b/jogos_2026-06-01.xlsx
@@ -1160,7 +1160,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Macará</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,64 +1202,64 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>2.45</v>
+        <v>3</v>
       </c>
       <c r="O5" t="n">
         <v>2.9</v>
       </c>
       <c r="P5" t="n">
-        <v>2.6</v>
+        <v>2.34</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.45</v>
+        <v>3.65</v>
       </c>
       <c r="R5" t="n">
-        <v>1.82</v>
+        <v>1.95</v>
       </c>
       <c r="S5" t="n">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="T5" t="n">
-        <v>2.31</v>
+        <v>2.26</v>
       </c>
       <c r="U5" t="n">
-        <v>3.7</v>
+        <v>3.4</v>
       </c>
       <c r="V5" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="W5" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="X5" t="n">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.45</v>
+        <v>1.54</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.7</v>
+        <v>2.45</v>
       </c>
       <c r="AA5" t="n">
         <v>2.45</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.57</v>
+        <v>1.44</v>
       </c>
       <c r="AC5" t="n">
         <v>4.8</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.91</v>
+        <v>2.17</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.77</v>
+        <v>1.67</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="AK5" t="n">
-        <v>1.46</v>
+        <v>1.33</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1319,7 +1319,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Macará</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,64 +1361,64 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>3.06</v>
+        <v>2.45</v>
       </c>
       <c r="O6" t="n">
-        <v>2.9</v>
+        <v>2.83</v>
       </c>
       <c r="P6" t="n">
-        <v>2.4</v>
+        <v>2.81</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.65</v>
+        <v>3.4</v>
       </c>
       <c r="R6" t="n">
-        <v>1.95</v>
+        <v>1.82</v>
       </c>
       <c r="S6" t="n">
-        <v>1.5</v>
+        <v>1.56</v>
       </c>
       <c r="T6" t="n">
-        <v>2.26</v>
+        <v>2.31</v>
       </c>
       <c r="U6" t="n">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
       <c r="V6" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="W6" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="X6" t="n">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.54</v>
+        <v>1.48</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.45</v>
+        <v>2.65</v>
       </c>
       <c r="AA6" t="n">
         <v>2.45</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.44</v>
+        <v>1.57</v>
       </c>
       <c r="AC6" t="n">
         <v>4.8</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="AF6" t="n">
-        <v>2.17</v>
+        <v>1.93</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1434,7 +1434,7 @@
         <v>1.36</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Barra do Garcas</t>
+          <t>Deportes Santa Cruz</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Copiapó</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,64 +1520,64 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>2.03</v>
+        <v>2.15</v>
       </c>
       <c r="O7" t="n">
-        <v>2.85</v>
+        <v>3.24</v>
       </c>
       <c r="P7" t="n">
-        <v>3.72</v>
+        <v>2.93</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.82</v>
+        <v>2.81</v>
       </c>
       <c r="R7" t="n">
-        <v>1.82</v>
+        <v>2.07</v>
       </c>
       <c r="S7" t="n">
-        <v>1.54</v>
+        <v>1.35</v>
       </c>
       <c r="T7" t="n">
-        <v>2.28</v>
+        <v>2.7</v>
       </c>
       <c r="U7" t="n">
-        <v>3.5</v>
+        <v>2.8</v>
       </c>
       <c r="V7" t="n">
-        <v>1.22</v>
+        <v>1.36</v>
       </c>
       <c r="W7" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="X7" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.43</v>
+        <v>1.27</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.46</v>
+        <v>3.14</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.44</v>
+        <v>1.93</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.48</v>
+        <v>1.78</v>
       </c>
       <c r="AC7" t="n">
-        <v>4.7</v>
+        <v>3.4</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.12</v>
+        <v>1.25</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="AF7" t="n">
-        <v>2.04</v>
+        <v>1.73</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.66</v>
+        <v>1.98</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.31</v>
+        <v>1.25</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.62</v>
+        <v>1.53</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Deportes Santa Cruz</t>
+          <t>Curicó Unido</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Copiapó</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,64 +1679,64 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>2.15</v>
+        <v>2.49</v>
       </c>
       <c r="O8" t="n">
-        <v>3.2</v>
+        <v>3.28</v>
       </c>
       <c r="P8" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="R8" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="S8" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="U8" t="n">
         <v>2.62</v>
       </c>
-      <c r="Q8" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="R8" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="S8" t="n">
+      <c r="V8" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X8" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>3.72</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="AD8" t="n">
         <v>1.35</v>
       </c>
-      <c r="T8" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="U8" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="V8" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="W8" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X8" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>1.29</v>
-      </c>
       <c r="AE8" t="n">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.73</v>
+        <v>1.65</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.98</v>
+        <v>2.19</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.25</v>
+        <v>1.45</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Curicó Unido</t>
+          <t>Barra do Garcas</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,64 +1838,64 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>2.45</v>
+        <v>2.03</v>
       </c>
       <c r="O9" t="n">
-        <v>3.25</v>
+        <v>2.85</v>
       </c>
       <c r="P9" t="n">
-        <v>2.45</v>
+        <v>3.72</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.06</v>
+        <v>2.82</v>
       </c>
       <c r="R9" t="n">
-        <v>2.1</v>
+        <v>1.82</v>
       </c>
       <c r="S9" t="n">
-        <v>1.33</v>
+        <v>1.54</v>
       </c>
       <c r="T9" t="n">
-        <v>2.9</v>
+        <v>2.28</v>
       </c>
       <c r="U9" t="n">
-        <v>2.65</v>
+        <v>3.5</v>
       </c>
       <c r="V9" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="W9" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X9" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y9" t="n">
         <v>1.43</v>
       </c>
-      <c r="W9" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="X9" t="n">
+      <c r="Z9" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AE9" t="n">
         <v>1.01</v>
       </c>
-      <c r="Y9" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>3.58</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>1.09</v>
-      </c>
       <c r="AF9" t="n">
-        <v>1.65</v>
+        <v>2.04</v>
       </c>
       <c r="AG9" t="n">
-        <v>2.16</v>
+        <v>1.66</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.43</v>
+        <v>1.62</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -2159,10 +2159,10 @@
         <v>2.91</v>
       </c>
       <c r="O11" t="n">
-        <v>2.87</v>
+        <v>2.9</v>
       </c>
       <c r="P11" t="n">
-        <v>2.17</v>
+        <v>2.35</v>
       </c>
       <c r="Q11" t="n">
         <v>3.45</v>
@@ -2174,7 +2174,7 @@
         <v>1.5</v>
       </c>
       <c r="T11" t="n">
-        <v>1.98</v>
+        <v>2.28</v>
       </c>
       <c r="U11" t="n">
         <v>3.4</v>
@@ -2183,7 +2183,7 @@
         <v>1.22</v>
       </c>
       <c r="W11" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="X11" t="n">
         <v>1.06</v>
@@ -2192,7 +2192,7 @@
         <v>1.4</v>
       </c>
       <c r="Z11" t="n">
-        <v>2.4</v>
+        <v>2.56</v>
       </c>
       <c r="AA11" t="n">
         <v>2.49</v>
@@ -2204,7 +2204,7 @@
         <v>4.8</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="AE11" t="n">
         <v>1.04</v>

--- a/jogos_2026-06-01.xlsx
+++ b/jogos_2026-06-01.xlsx
@@ -1160,7 +1160,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Macará</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,64 +1202,64 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>3</v>
+        <v>2.45</v>
       </c>
       <c r="O5" t="n">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="P5" t="n">
-        <v>2.34</v>
+        <v>2.35</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.65</v>
+        <v>3.35</v>
       </c>
       <c r="R5" t="n">
-        <v>1.95</v>
+        <v>1.81</v>
       </c>
       <c r="S5" t="n">
-        <v>1.5</v>
+        <v>1.56</v>
       </c>
       <c r="T5" t="n">
-        <v>2.26</v>
+        <v>2.31</v>
       </c>
       <c r="U5" t="n">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
       <c r="V5" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="W5" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="X5" t="n">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.54</v>
+        <v>1.45</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.45</v>
+        <v>2.7</v>
       </c>
       <c r="AA5" t="n">
         <v>2.45</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.44</v>
+        <v>1.57</v>
       </c>
       <c r="AC5" t="n">
         <v>4.8</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="AF5" t="n">
-        <v>2.17</v>
+        <v>1.91</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="AK5" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1319,7 +1319,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Macará</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,64 +1361,64 @@
         </is>
       </c>
       <c r="N6" t="n">
+        <v>3</v>
+      </c>
+      <c r="O6" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="P6" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="S6" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="T6" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="U6" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="V6" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="W6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X6" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="Z6" t="n">
         <v>2.45</v>
-      </c>
-      <c r="O6" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="P6" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="R6" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="S6" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="T6" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="U6" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="V6" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="W6" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X6" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>2.65</v>
       </c>
       <c r="AA6" t="n">
         <v>2.45</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.57</v>
+        <v>1.44</v>
       </c>
       <c r="AC6" t="n">
         <v>4.8</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.93</v>
+        <v>2.17</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1434,7 +1434,7 @@
         <v>1.36</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Deportes Santa Cruz</t>
+          <t>Curicó Unido</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Copiapó</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,64 +1520,64 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>2.15</v>
+        <v>2.47</v>
       </c>
       <c r="O7" t="n">
-        <v>3.24</v>
+        <v>3.3</v>
       </c>
       <c r="P7" t="n">
-        <v>2.93</v>
+        <v>2.45</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.81</v>
+        <v>3.04</v>
       </c>
       <c r="R7" t="n">
-        <v>2.07</v>
+        <v>2.14</v>
       </c>
       <c r="S7" t="n">
-        <v>1.35</v>
+        <v>1.31</v>
       </c>
       <c r="T7" t="n">
-        <v>2.7</v>
+        <v>3.02</v>
       </c>
       <c r="U7" t="n">
-        <v>2.8</v>
+        <v>2.5</v>
       </c>
       <c r="V7" t="n">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="W7" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="X7" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.27</v>
+        <v>1.18</v>
       </c>
       <c r="Z7" t="n">
-        <v>3.14</v>
+        <v>3.84</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.93</v>
+        <v>1.7</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.78</v>
+        <v>2.03</v>
       </c>
       <c r="AC7" t="n">
-        <v>3.4</v>
+        <v>2.88</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.25</v>
+        <v>1.37</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.73</v>
+        <v>1.65</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.98</v>
+        <v>2.25</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.53</v>
+        <v>1.42</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Curicó Unido</t>
+          <t>Barra do Garcas</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,65 +1679,65 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>2.49</v>
+        <v>1.9</v>
       </c>
       <c r="O8" t="n">
-        <v>3.28</v>
+        <v>3</v>
       </c>
       <c r="P8" t="n">
-        <v>2.48</v>
+        <v>3.99</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.1</v>
+        <v>2.63</v>
       </c>
       <c r="R8" t="n">
-        <v>2.12</v>
+        <v>1.85</v>
       </c>
       <c r="S8" t="n">
-        <v>1.33</v>
+        <v>1.53</v>
       </c>
       <c r="T8" t="n">
-        <v>2.91</v>
+        <v>2.31</v>
       </c>
       <c r="U8" t="n">
-        <v>2.62</v>
+        <v>3.5</v>
       </c>
       <c r="V8" t="n">
-        <v>1.43</v>
+        <v>1.25</v>
       </c>
       <c r="W8" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="X8" t="n">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.2</v>
+        <v>1.41</v>
       </c>
       <c r="Z8" t="n">
-        <v>3.72</v>
+        <v>2.52</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.74</v>
+        <v>2.38</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.98</v>
+        <v>1.5</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.93</v>
+        <v>4.55</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.35</v>
+        <v>1.13</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.1</v>
+        <v>1.02</v>
       </c>
       <c r="AF8" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AG8" t="n">
         <v>1.65</v>
       </c>
-      <c r="AG8" t="n">
-        <v>2.19</v>
-      </c>
       <c r="AH8" t="inlineStr">
         <is>
           <t>[]</t>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.45</v>
+        <v>1.29</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.44</v>
+        <v>1.73</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Barra do Garcas</t>
+          <t>Deportes Santa Cruz</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Copiapó</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,64 +1838,64 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>2.03</v>
+        <v>2.21</v>
       </c>
       <c r="O9" t="n">
-        <v>2.85</v>
+        <v>3.25</v>
       </c>
       <c r="P9" t="n">
-        <v>3.72</v>
+        <v>2.94</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.82</v>
+        <v>2.88</v>
       </c>
       <c r="R9" t="n">
-        <v>1.82</v>
+        <v>2.07</v>
       </c>
       <c r="S9" t="n">
-        <v>1.54</v>
+        <v>1.35</v>
       </c>
       <c r="T9" t="n">
-        <v>2.28</v>
+        <v>2.74</v>
       </c>
       <c r="U9" t="n">
-        <v>3.5</v>
+        <v>2.8</v>
       </c>
       <c r="V9" t="n">
-        <v>1.22</v>
+        <v>1.36</v>
       </c>
       <c r="W9" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="X9" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.43</v>
+        <v>1.29</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.46</v>
+        <v>3.14</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.44</v>
+        <v>1.92</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.48</v>
+        <v>1.79</v>
       </c>
       <c r="AC9" t="n">
-        <v>4.7</v>
+        <v>3.4</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.12</v>
+        <v>1.26</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="AF9" t="n">
-        <v>2.04</v>
+        <v>1.72</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.66</v>
+        <v>1.98</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1.31</v>
+        <v>1.25</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.62</v>
+        <v>1.53</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -2000,16 +2000,16 @@
         <v>2.1</v>
       </c>
       <c r="O10" t="n">
-        <v>3.4</v>
+        <v>3.15</v>
       </c>
       <c r="P10" t="n">
-        <v>2.85</v>
+        <v>3.01</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.8</v>
+        <v>2.76</v>
       </c>
       <c r="R10" t="n">
-        <v>2.3</v>
+        <v>2.12</v>
       </c>
       <c r="S10" t="n">
         <v>1.32</v>
@@ -2039,10 +2039,10 @@
         <v>1.62</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.16</v>
+        <v>2.25</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.63</v>
+        <v>2.39</v>
       </c>
       <c r="AD10" t="n">
         <v>1.45</v>
@@ -2051,7 +2051,7 @@
         <v>1.15</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="AG10" t="n">
         <v>2.36</v>
@@ -2162,7 +2162,7 @@
         <v>2.9</v>
       </c>
       <c r="P11" t="n">
-        <v>2.35</v>
+        <v>2.37</v>
       </c>
       <c r="Q11" t="n">
         <v>3.45</v>
@@ -2192,7 +2192,7 @@
         <v>1.4</v>
       </c>
       <c r="Z11" t="n">
-        <v>2.56</v>
+        <v>2.4</v>
       </c>
       <c r="AA11" t="n">
         <v>2.49</v>
@@ -2204,7 +2204,7 @@
         <v>4.8</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="AE11" t="n">
         <v>1.04</v>

--- a/jogos_2026-06-01.xlsx
+++ b/jogos_2026-06-01.xlsx
@@ -734,13 +734,13 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.22</v>
+        <v>2.88</v>
       </c>
       <c r="R2" t="n">
         <v>1.86</v>
       </c>
       <c r="S2" t="n">
-        <v>1.51</v>
+        <v>1.49</v>
       </c>
       <c r="T2" t="n">
         <v>2.36</v>
@@ -770,7 +770,7 @@
         <v>1.55</v>
       </c>
       <c r="AC2" t="n">
-        <v>4.25</v>
+        <v>4.5</v>
       </c>
       <c r="AD2" t="n">
         <v>1.15</v>
@@ -884,37 +884,37 @@
         </is>
       </c>
       <c r="N3" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="O3" t="n">
         <v>2.75</v>
       </c>
-      <c r="O3" t="n">
-        <v>2.72</v>
-      </c>
       <c r="P3" t="n">
-        <v>2.6</v>
+        <v>2.3</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.3</v>
+        <v>3.48</v>
       </c>
       <c r="R3" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="S3" t="n">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="T3" t="n">
-        <v>2.15</v>
+        <v>2.07</v>
       </c>
       <c r="U3" t="n">
-        <v>3.78</v>
+        <v>4.1</v>
       </c>
       <c r="V3" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="W3" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X3" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="Y3" t="n">
         <v>1.57</v>
@@ -923,19 +923,19 @@
         <v>2.33</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.84</v>
+        <v>2.9</v>
       </c>
       <c r="AB3" t="n">
         <v>1.38</v>
       </c>
       <c r="AC3" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AF3" t="n">
         <v>2.15</v>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="AJ3" t="n">
-        <v>1.35</v>
+        <v>1.39</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.33</v>
+        <v>1.26</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -1043,13 +1043,13 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="O4" t="n">
-        <v>2.85</v>
+        <v>2.8</v>
       </c>
       <c r="P4" t="n">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="Q4" t="n">
         <v>2.64</v>
@@ -1058,49 +1058,49 @@
         <v>1.8</v>
       </c>
       <c r="S4" t="n">
-        <v>1.47</v>
+        <v>1.6</v>
       </c>
       <c r="T4" t="n">
-        <v>2.33</v>
+        <v>2.18</v>
       </c>
       <c r="U4" t="n">
-        <v>3.92</v>
+        <v>4.1</v>
       </c>
       <c r="V4" t="n">
         <v>1.18</v>
       </c>
       <c r="W4" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X4" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.59</v>
+        <v>1.56</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.29</v>
+        <v>2.22</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.85</v>
+        <v>2.75</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="AC4" t="n">
-        <v>5.5</v>
+        <v>5.75</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AE4" t="n">
         <v>1.01</v>
       </c>
       <c r="AF4" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1116,7 +1116,7 @@
         <v>1.32</v>
       </c>
       <c r="AK4" t="n">
-        <v>1.65</v>
+        <v>1.57</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Barra do Garcas</t>
+          <t>Deportes Santa Cruz</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Copiapó</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,80 +1679,80 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1.9</v>
+        <v>2.21</v>
       </c>
       <c r="O8" t="n">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="P8" t="n">
-        <v>3.99</v>
+        <v>2.94</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.63</v>
+        <v>2.88</v>
       </c>
       <c r="R8" t="n">
-        <v>1.85</v>
+        <v>2.07</v>
       </c>
       <c r="S8" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="U8" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="V8" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X8" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ8" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AK8" t="n">
         <v>1.53</v>
-      </c>
-      <c r="T8" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="U8" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="V8" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="W8" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X8" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>4.55</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ8" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>1.73</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Deportes Santa Cruz</t>
+          <t>Barra do Garcas</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Copiapó</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,80 +1838,80 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>2.21</v>
+        <v>1.9</v>
       </c>
       <c r="O9" t="n">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="P9" t="n">
-        <v>2.94</v>
+        <v>3.99</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.88</v>
+        <v>2.63</v>
       </c>
       <c r="R9" t="n">
-        <v>2.07</v>
+        <v>1.85</v>
       </c>
       <c r="S9" t="n">
-        <v>1.35</v>
+        <v>1.53</v>
       </c>
       <c r="T9" t="n">
-        <v>2.74</v>
+        <v>2.31</v>
       </c>
       <c r="U9" t="n">
-        <v>2.8</v>
+        <v>3.5</v>
       </c>
       <c r="V9" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="W9" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="X9" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y9" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>4.55</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ9" t="n">
         <v>1.29</v>
       </c>
-      <c r="Z9" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ9" t="n">
-        <v>1.25</v>
-      </c>
       <c r="AK9" t="n">
-        <v>1.53</v>
+        <v>1.73</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>

--- a/jogos_2026-06-01.xlsx
+++ b/jogos_2026-06-01.xlsx
@@ -1160,7 +1160,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Macará</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,64 +1202,64 @@
         </is>
       </c>
       <c r="N5" t="n">
+        <v>3</v>
+      </c>
+      <c r="O5" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="P5" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="S5" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="U5" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="V5" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="W5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X5" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="Z5" t="n">
         <v>2.45</v>
-      </c>
-      <c r="O5" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="P5" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="R5" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="S5" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="T5" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="U5" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="V5" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="W5" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X5" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>2.7</v>
       </c>
       <c r="AA5" t="n">
         <v>2.45</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.57</v>
+        <v>1.44</v>
       </c>
       <c r="AC5" t="n">
         <v>4.8</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.91</v>
+        <v>2.17</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.77</v>
+        <v>1.67</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AK5" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1319,7 +1319,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Macará</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,64 +1361,64 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>3</v>
+        <v>2.45</v>
       </c>
       <c r="O6" t="n">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="P6" t="n">
-        <v>2.26</v>
+        <v>2.35</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.65</v>
+        <v>3.35</v>
       </c>
       <c r="R6" t="n">
-        <v>1.95</v>
+        <v>1.81</v>
       </c>
       <c r="S6" t="n">
-        <v>1.5</v>
+        <v>1.56</v>
       </c>
       <c r="T6" t="n">
-        <v>2.26</v>
+        <v>2.31</v>
       </c>
       <c r="U6" t="n">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
       <c r="V6" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="W6" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="X6" t="n">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.54</v>
+        <v>1.45</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.45</v>
+        <v>2.7</v>
       </c>
       <c r="AA6" t="n">
         <v>2.45</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.44</v>
+        <v>1.57</v>
       </c>
       <c r="AC6" t="n">
         <v>4.8</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="AF6" t="n">
-        <v>2.17</v>
+        <v>1.91</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Deportes Santa Cruz</t>
+          <t>Barra do Garcas</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Copiapó</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,80 +1679,80 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>2.21</v>
+        <v>1.9</v>
       </c>
       <c r="O8" t="n">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="P8" t="n">
-        <v>2.94</v>
+        <v>3.99</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.88</v>
+        <v>2.63</v>
       </c>
       <c r="R8" t="n">
-        <v>2.07</v>
+        <v>1.85</v>
       </c>
       <c r="S8" t="n">
-        <v>1.35</v>
+        <v>1.53</v>
       </c>
       <c r="T8" t="n">
-        <v>2.74</v>
+        <v>2.31</v>
       </c>
       <c r="U8" t="n">
-        <v>2.8</v>
+        <v>3.5</v>
       </c>
       <c r="V8" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="W8" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="X8" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y8" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>4.55</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ8" t="n">
         <v>1.29</v>
       </c>
-      <c r="Z8" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ8" t="n">
-        <v>1.25</v>
-      </c>
       <c r="AK8" t="n">
-        <v>1.53</v>
+        <v>1.73</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Barra do Garcas</t>
+          <t>Deportes Santa Cruz</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Copiapó</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,80 +1838,80 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>1.9</v>
+        <v>2.21</v>
       </c>
       <c r="O9" t="n">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="P9" t="n">
-        <v>3.99</v>
+        <v>2.94</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.63</v>
+        <v>2.88</v>
       </c>
       <c r="R9" t="n">
-        <v>1.85</v>
+        <v>2.07</v>
       </c>
       <c r="S9" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="U9" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="V9" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="W9" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ9" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AK9" t="n">
         <v>1.53</v>
-      </c>
-      <c r="T9" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="U9" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="V9" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="W9" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X9" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>4.55</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ9" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AK9" t="n">
-        <v>1.73</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>

--- a/jogos_2026-06-01.xlsx
+++ b/jogos_2026-06-01.xlsx
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Curicó Unido</t>
+          <t>Deportes Santa Cruz</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Copiapó</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,64 +1520,64 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>2.47</v>
+        <v>2.21</v>
       </c>
       <c r="O7" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="P7" t="n">
-        <v>2.45</v>
+        <v>2.94</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.04</v>
+        <v>2.88</v>
       </c>
       <c r="R7" t="n">
-        <v>2.14</v>
+        <v>2.07</v>
       </c>
       <c r="S7" t="n">
-        <v>1.31</v>
+        <v>1.35</v>
       </c>
       <c r="T7" t="n">
-        <v>3.02</v>
+        <v>2.74</v>
       </c>
       <c r="U7" t="n">
-        <v>2.5</v>
+        <v>2.8</v>
       </c>
       <c r="V7" t="n">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="W7" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="X7" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.18</v>
+        <v>1.29</v>
       </c>
       <c r="Z7" t="n">
-        <v>3.84</v>
+        <v>3.14</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.7</v>
+        <v>1.92</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.03</v>
+        <v>1.79</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.88</v>
+        <v>3.4</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.37</v>
+        <v>1.26</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.65</v>
+        <v>1.72</v>
       </c>
       <c r="AG7" t="n">
-        <v>2.25</v>
+        <v>1.98</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.42</v>
+        <v>1.53</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Deportes Santa Cruz</t>
+          <t>Curicó Unido</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Copiapó</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,64 +1838,64 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>2.21</v>
+        <v>2.47</v>
       </c>
       <c r="O9" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="P9" t="n">
-        <v>2.94</v>
+        <v>2.45</v>
       </c>
       <c r="Q9" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="R9" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="S9" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="T9" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="U9" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="V9" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="W9" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X9" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>3.84</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AC9" t="n">
         <v>2.88</v>
       </c>
-      <c r="R9" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="S9" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="T9" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="U9" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="V9" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="W9" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X9" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>3.4</v>
-      </c>
       <c r="AD9" t="n">
-        <v>1.26</v>
+        <v>1.37</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.72</v>
+        <v>1.65</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.98</v>
+        <v>2.25</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.53</v>
+        <v>1.42</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>

--- a/jogos_2026-06-01.xlsx
+++ b/jogos_2026-06-01.xlsx
@@ -1361,64 +1361,64 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>2.45</v>
+        <v>2.55</v>
       </c>
       <c r="O6" t="n">
-        <v>2.88</v>
+        <v>2.8</v>
       </c>
       <c r="P6" t="n">
-        <v>2.35</v>
+        <v>2.69</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="R6" t="n">
-        <v>1.81</v>
+        <v>1.95</v>
       </c>
       <c r="S6" t="n">
-        <v>1.56</v>
+        <v>1.59</v>
       </c>
       <c r="T6" t="n">
-        <v>2.31</v>
+        <v>2.25</v>
       </c>
       <c r="U6" t="n">
-        <v>3.7</v>
+        <v>3.4</v>
       </c>
       <c r="V6" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="W6" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X6" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>5</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AE6" t="n">
         <v>1.04</v>
       </c>
-      <c r="X6" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>1.05</v>
-      </c>
       <c r="AF6" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.77</v>
+        <v>1.7</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1434,7 +1434,7 @@
         <v>1.38</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1679,31 +1679,31 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="O8" t="n">
-        <v>3</v>
+        <v>3.04</v>
       </c>
       <c r="P8" t="n">
-        <v>3.99</v>
+        <v>3.93</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.63</v>
+        <v>2.67</v>
       </c>
       <c r="R8" t="n">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="S8" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="T8" t="n">
-        <v>2.31</v>
+        <v>2.42</v>
       </c>
       <c r="U8" t="n">
-        <v>3.5</v>
+        <v>3.42</v>
       </c>
       <c r="V8" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="W8" t="n">
         <v>1.03</v>
@@ -1712,19 +1712,19 @@
         <v>1.04</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.41</v>
+        <v>1.47</v>
       </c>
       <c r="Z8" t="n">
         <v>2.52</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.38</v>
+        <v>2.34</v>
       </c>
       <c r="AB8" t="n">
         <v>1.5</v>
       </c>
       <c r="AC8" t="n">
-        <v>4.55</v>
+        <v>5</v>
       </c>
       <c r="AD8" t="n">
         <v>1.13</v>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1997,34 +1997,34 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>2.1</v>
+        <v>2.4</v>
       </c>
       <c r="O10" t="n">
-        <v>3.15</v>
+        <v>3.45</v>
       </c>
       <c r="P10" t="n">
-        <v>3.01</v>
+        <v>2.58</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.76</v>
+        <v>2.98</v>
       </c>
       <c r="R10" t="n">
-        <v>2.12</v>
+        <v>2.24</v>
       </c>
       <c r="S10" t="n">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="T10" t="n">
-        <v>2.96</v>
+        <v>3.25</v>
       </c>
       <c r="U10" t="n">
-        <v>2.33</v>
+        <v>2.36</v>
       </c>
       <c r="V10" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="W10" t="n">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="X10" t="n">
         <v>1</v>
@@ -2039,16 +2039,16 @@
         <v>1.62</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.25</v>
+        <v>2.16</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.39</v>
+        <v>2.42</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AF10" t="n">
         <v>1.51</v>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AK10" t="n">
-        <v>1.55</v>
+        <v>1.43</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>

--- a/jogos_2026-06-01.xlsx
+++ b/jogos_2026-06-01.xlsx
@@ -721,68 +721,68 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.88</v>
+        <v>3.54</v>
       </c>
       <c r="R2" t="n">
-        <v>1.86</v>
+        <v>1.83</v>
       </c>
       <c r="S2" t="n">
-        <v>1.49</v>
+        <v>1.54</v>
       </c>
       <c r="T2" t="n">
-        <v>2.36</v>
+        <v>2.32</v>
       </c>
       <c r="U2" t="n">
-        <v>3.32</v>
+        <v>3.6</v>
       </c>
       <c r="V2" t="n">
-        <v>1.26</v>
+        <v>1.23</v>
       </c>
       <c r="W2" t="n">
         <v>1.03</v>
       </c>
       <c r="X2" t="n">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.38</v>
+        <v>1.45</v>
       </c>
       <c r="Z2" t="n">
-        <v>2.62</v>
+        <v>2.61</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.33</v>
+        <v>2.5</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AC2" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.92</v>
+        <v>1.97</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.77</v>
+        <v>1.73</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -795,37 +795,37 @@
         </is>
       </c>
       <c r="AJ2" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="AK2" t="n">
-        <v>1.44</v>
+        <v>1.37</v>
       </c>
       <c r="AL2" t="n">
         <v>0</v>
       </c>
       <c r="AM2" t="n">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AN2" t="n">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AO2" t="n">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AP2" t="n">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AR2" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AS2" t="n">
-        <v>0</v>
+        <v>130</v>
       </c>
       <c r="AT2" t="n">
-        <v>0</v>
+        <v>98</v>
       </c>
       <c r="AU2" s="3" t="n">
         <v>46174.54166666666</v>
@@ -884,64 +884,64 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>3.1</v>
+        <v>2.7</v>
       </c>
       <c r="O3" t="n">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="P3" t="n">
-        <v>2.3</v>
+        <v>2.7</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.48</v>
+        <v>3.55</v>
       </c>
       <c r="R3" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="S3" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="T3" t="n">
-        <v>2.07</v>
+        <v>2.1</v>
       </c>
       <c r="U3" t="n">
-        <v>4.1</v>
+        <v>3.8</v>
       </c>
       <c r="V3" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="W3" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X3" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.33</v>
+        <v>2.51</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.9</v>
+        <v>2.67</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="AC3" t="n">
-        <v>5.5</v>
+        <v>5.25</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="AF3" t="n">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.61</v>
+        <v>1.71</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="AJ3" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.26</v>
+        <v>1.32</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -1043,55 +1043,55 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="O4" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="P4" t="n">
-        <v>3.5</v>
+        <v>3.84</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.64</v>
+        <v>2.69</v>
       </c>
       <c r="R4" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="S4" t="n">
-        <v>1.6</v>
+        <v>1.56</v>
       </c>
       <c r="T4" t="n">
-        <v>2.18</v>
+        <v>2.26</v>
       </c>
       <c r="U4" t="n">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="V4" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="W4" t="n">
         <v>1.02</v>
       </c>
       <c r="X4" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.22</v>
+        <v>2.41</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AC4" t="n">
-        <v>5.75</v>
+        <v>5.5</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AE4" t="n">
         <v>1.01</v>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="AK4" t="n">
-        <v>1.57</v>
+        <v>1.7</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1202,16 +1202,16 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>3</v>
+        <v>2.55</v>
       </c>
       <c r="O5" t="n">
-        <v>2.9</v>
+        <v>2.96</v>
       </c>
       <c r="P5" t="n">
-        <v>2.26</v>
+        <v>2.7</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.65</v>
+        <v>3.3</v>
       </c>
       <c r="R5" t="n">
         <v>1.95</v>
@@ -1220,7 +1220,7 @@
         <v>1.5</v>
       </c>
       <c r="T5" t="n">
-        <v>2.26</v>
+        <v>2.31</v>
       </c>
       <c r="U5" t="n">
         <v>3.4</v>
@@ -1232,22 +1232,22 @@
         <v>1.01</v>
       </c>
       <c r="X5" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="Y5" t="n">
         <v>1.54</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="AA5" t="n">
         <v>2.45</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AC5" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="AD5" t="n">
         <v>1.14</v>
@@ -1275,7 +1275,7 @@
         <v>1.36</v>
       </c>
       <c r="AK5" t="n">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1520,80 +1520,80 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>2.21</v>
+        <v>2.09</v>
       </c>
       <c r="O7" t="n">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="P7" t="n">
-        <v>2.94</v>
+        <v>3</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.88</v>
+        <v>2.8</v>
       </c>
       <c r="R7" t="n">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="S7" t="n">
         <v>1.35</v>
       </c>
       <c r="T7" t="n">
-        <v>2.74</v>
+        <v>2.66</v>
       </c>
       <c r="U7" t="n">
-        <v>2.8</v>
+        <v>2.89</v>
       </c>
       <c r="V7" t="n">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="W7" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X7" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="Z7" t="n">
-        <v>3.14</v>
+        <v>3.25</v>
       </c>
       <c r="AA7" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AG7" t="n">
         <v>1.92</v>
       </c>
-      <c r="AB7" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AD7" t="n">
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ7" t="n">
         <v>1.26</v>
       </c>
-      <c r="AE7" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ7" t="n">
-        <v>1.25</v>
-      </c>
       <c r="AK7" t="n">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Barra do Garcas</t>
+          <t>Curicó Unido</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,64 +1679,64 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1.92</v>
+        <v>2.47</v>
       </c>
       <c r="O8" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="P8" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="Q8" t="n">
         <v>3.04</v>
       </c>
-      <c r="P8" t="n">
-        <v>3.93</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>2.67</v>
-      </c>
       <c r="R8" t="n">
-        <v>1.87</v>
+        <v>2.14</v>
       </c>
       <c r="S8" t="n">
-        <v>1.52</v>
+        <v>1.31</v>
       </c>
       <c r="T8" t="n">
-        <v>2.42</v>
+        <v>3.02</v>
       </c>
       <c r="U8" t="n">
-        <v>3.42</v>
+        <v>2.5</v>
       </c>
       <c r="V8" t="n">
-        <v>1.24</v>
+        <v>1.44</v>
       </c>
       <c r="W8" t="n">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="X8" t="n">
         <v>1.04</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.47</v>
+        <v>1.22</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.52</v>
+        <v>3.84</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.34</v>
+        <v>1.7</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.5</v>
+        <v>2.03</v>
       </c>
       <c r="AC8" t="n">
-        <v>5</v>
+        <v>2.88</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.13</v>
+        <v>1.37</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.02</v>
+        <v>1.11</v>
       </c>
       <c r="AF8" t="n">
-        <v>2.06</v>
+        <v>1.52</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.65</v>
+        <v>2.25</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.28</v>
+        <v>1.24</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.7</v>
+        <v>1.42</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Curicó Unido</t>
+          <t>Barra do Garcas</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,80 +1838,80 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>2.47</v>
+        <v>1.92</v>
       </c>
       <c r="O9" t="n">
-        <v>3.3</v>
+        <v>3.04</v>
       </c>
       <c r="P9" t="n">
-        <v>2.45</v>
+        <v>3.93</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.04</v>
+        <v>2.67</v>
       </c>
       <c r="R9" t="n">
-        <v>2.14</v>
+        <v>1.87</v>
       </c>
       <c r="S9" t="n">
-        <v>1.31</v>
+        <v>1.52</v>
       </c>
       <c r="T9" t="n">
-        <v>3.02</v>
+        <v>2.42</v>
       </c>
       <c r="U9" t="n">
-        <v>2.5</v>
+        <v>3.42</v>
       </c>
       <c r="V9" t="n">
-        <v>1.44</v>
+        <v>1.24</v>
       </c>
       <c r="W9" t="n">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="X9" t="n">
         <v>1.04</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.18</v>
+        <v>1.47</v>
       </c>
       <c r="Z9" t="n">
-        <v>3.84</v>
+        <v>2.52</v>
       </c>
       <c r="AA9" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>5</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ9" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AK9" t="n">
         <v>1.7</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ9" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AK9" t="n">
-        <v>1.42</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -2159,10 +2159,10 @@
         <v>2.91</v>
       </c>
       <c r="O11" t="n">
-        <v>2.9</v>
+        <v>2.93</v>
       </c>
       <c r="P11" t="n">
-        <v>2.37</v>
+        <v>2.55</v>
       </c>
       <c r="Q11" t="n">
         <v>3.45</v>
@@ -2174,46 +2174,46 @@
         <v>1.5</v>
       </c>
       <c r="T11" t="n">
-        <v>2.28</v>
+        <v>2.36</v>
       </c>
       <c r="U11" t="n">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="V11" t="n">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="W11" t="n">
         <v>1.01</v>
       </c>
       <c r="X11" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="Y11" t="n">
         <v>1.4</v>
       </c>
       <c r="Z11" t="n">
-        <v>2.4</v>
+        <v>2.63</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.49</v>
+        <v>2.3</v>
       </c>
       <c r="AB11" t="n">
         <v>1.5</v>
       </c>
       <c r="AC11" t="n">
-        <v>4.8</v>
+        <v>4.33</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,7 +2226,7 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="AK11" t="n">
         <v>1.36</v>

--- a/jogos_2026-06-01.xlsx
+++ b/jogos_2026-06-01.xlsx
@@ -861,26 +861,26 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N3" t="n">
@@ -945,12 +945,12 @@
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['51']</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['45+2', '52']</t>
         </is>
       </c>
       <c r="AJ3" t="n">
@@ -963,28 +963,28 @@
         <v>0</v>
       </c>
       <c r="AM3" t="n">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AN3" t="n">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO3" t="n">
-        <v>-1</v>
+        <v>13</v>
       </c>
       <c r="AP3" t="n">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AR3" t="n">
-        <v>0</v>
+        <v>0.86</v>
       </c>
       <c r="AS3" t="n">
-        <v>0</v>
+        <v>94</v>
       </c>
       <c r="AT3" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="AU3" s="3" t="n">
         <v>46174.625</v>
@@ -1020,13 +1020,13 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
@@ -1035,27 +1035,27 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N4" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="O4" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="P4" t="n">
-        <v>3.84</v>
+        <v>4.33</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.69</v>
+        <v>2.38</v>
       </c>
       <c r="R4" t="n">
-        <v>1.81</v>
+        <v>1.84</v>
       </c>
       <c r="S4" t="n">
         <v>1.56</v>
@@ -1064,7 +1064,7 @@
         <v>2.26</v>
       </c>
       <c r="U4" t="n">
-        <v>3.9</v>
+        <v>3.55</v>
       </c>
       <c r="V4" t="n">
         <v>1.2</v>
@@ -1073,7 +1073,7 @@
         <v>1.02</v>
       </c>
       <c r="X4" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="Y4" t="n">
         <v>1.5</v>
@@ -1082,10 +1082,10 @@
         <v>2.41</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.7</v>
+        <v>2.49</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="AC4" t="n">
         <v>5.5</v>
@@ -1094,7 +1094,7 @@
         <v>1.11</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AF4" t="n">
         <v>2.25</v>
@@ -1104,46 +1104,46 @@
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['28', '31']</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['88']</t>
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AK4" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
       </c>
       <c r="AM4" t="n">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AN4" t="n">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO4" t="n">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AP4" t="n">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR4" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AS4" t="n">
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="AT4" t="n">
-        <v>0</v>
+        <v>82</v>
       </c>
       <c r="AU4" s="3" t="n">
         <v>46174.70833333334</v>
@@ -1160,7 +1160,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Macará</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,25 +1202,25 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>2.55</v>
+        <v>2.87</v>
       </c>
       <c r="O5" t="n">
-        <v>2.96</v>
+        <v>2.88</v>
       </c>
       <c r="P5" t="n">
-        <v>2.7</v>
+        <v>2.25</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.3</v>
+        <v>3.55</v>
       </c>
       <c r="R5" t="n">
         <v>1.95</v>
       </c>
       <c r="S5" t="n">
-        <v>1.5</v>
+        <v>1.59</v>
       </c>
       <c r="T5" t="n">
-        <v>2.31</v>
+        <v>2.25</v>
       </c>
       <c r="U5" t="n">
         <v>3.4</v>
@@ -1229,19 +1229,19 @@
         <v>1.23</v>
       </c>
       <c r="W5" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="X5" t="n">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="AB5" t="n">
         <v>1.5</v>
@@ -1250,16 +1250,16 @@
         <v>5</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="AE5" t="n">
         <v>1.04</v>
       </c>
       <c r="AF5" t="n">
-        <v>2.17</v>
+        <v>2</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="AJ5" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AK5" t="n">
         <v>1.36</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>1.44</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1319,7 +1319,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Macará</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,64 +1361,64 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>2.55</v>
+        <v>2.87</v>
       </c>
       <c r="O6" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="P6" t="n">
-        <v>2.69</v>
+        <v>2.45</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="R6" t="n">
         <v>1.95</v>
       </c>
       <c r="S6" t="n">
-        <v>1.59</v>
+        <v>1.5</v>
       </c>
       <c r="T6" t="n">
-        <v>2.25</v>
+        <v>2.31</v>
       </c>
       <c r="U6" t="n">
         <v>3.4</v>
       </c>
       <c r="V6" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="W6" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="X6" t="n">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.5</v>
+        <v>1.54</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AC6" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AE6" t="n">
         <v>1.04</v>
       </c>
       <c r="AF6" t="n">
-        <v>2</v>
+        <v>2.17</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1520,16 +1520,16 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>2.09</v>
+        <v>2.25</v>
       </c>
       <c r="O7" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="P7" t="n">
         <v>3</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.8</v>
+        <v>2.67</v>
       </c>
       <c r="R7" t="n">
         <v>2.05</v>
@@ -1550,13 +1550,13 @@
         <v>1.04</v>
       </c>
       <c r="X7" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="Z7" t="n">
-        <v>3.25</v>
+        <v>3.04</v>
       </c>
       <c r="AA7" t="n">
         <v>1.98</v>
@@ -1571,7 +1571,7 @@
         <v>1.24</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="AF7" t="n">
         <v>1.77</v>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Curicó Unido</t>
+          <t>Barra do Garcas</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,64 +1679,64 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>2.47</v>
+        <v>1.92</v>
       </c>
       <c r="O8" t="n">
-        <v>3.32</v>
+        <v>3.1</v>
       </c>
       <c r="P8" t="n">
-        <v>2.48</v>
+        <v>4.05</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.04</v>
+        <v>2.69</v>
       </c>
       <c r="R8" t="n">
-        <v>2.14</v>
+        <v>1.86</v>
       </c>
       <c r="S8" t="n">
-        <v>1.31</v>
+        <v>1.52</v>
       </c>
       <c r="T8" t="n">
-        <v>3.02</v>
+        <v>2.33</v>
       </c>
       <c r="U8" t="n">
-        <v>2.5</v>
+        <v>3.48</v>
       </c>
       <c r="V8" t="n">
-        <v>1.44</v>
+        <v>1.22</v>
       </c>
       <c r="W8" t="n">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="X8" t="n">
         <v>1.04</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.22</v>
+        <v>1.42</v>
       </c>
       <c r="Z8" t="n">
-        <v>3.84</v>
+        <v>2.49</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.7</v>
+        <v>2.5</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.03</v>
+        <v>1.5</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.88</v>
+        <v>5</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.37</v>
+        <v>1.12</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.11</v>
+        <v>1.02</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.52</v>
+        <v>2.08</v>
       </c>
       <c r="AG8" t="n">
-        <v>2.25</v>
+        <v>1.64</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.42</v>
+        <v>1.69</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Barra do Garcas</t>
+          <t>Curicó Unido</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,80 +1838,80 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>1.92</v>
+        <v>2.87</v>
       </c>
       <c r="O9" t="n">
-        <v>3.04</v>
+        <v>3.3</v>
       </c>
       <c r="P9" t="n">
-        <v>3.93</v>
+        <v>2.19</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.67</v>
+        <v>3.5</v>
       </c>
       <c r="R9" t="n">
-        <v>1.87</v>
+        <v>2.15</v>
       </c>
       <c r="S9" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="T9" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="U9" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="V9" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="W9" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>3.92</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AF9" t="n">
         <v>1.52</v>
       </c>
-      <c r="T9" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="U9" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="V9" t="n">
+      <c r="AG9" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ9" t="n">
         <v>1.24</v>
       </c>
-      <c r="W9" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X9" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>5</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ9" t="n">
-        <v>1.28</v>
-      </c>
       <c r="AK9" t="n">
-        <v>1.7</v>
+        <v>1.34</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1997,25 +1997,25 @@
         </is>
       </c>
       <c r="N10" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="O10" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="P10" t="n">
         <v>2.4</v>
       </c>
-      <c r="O10" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="P10" t="n">
-        <v>2.58</v>
-      </c>
       <c r="Q10" t="n">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="R10" t="n">
-        <v>2.24</v>
+        <v>2.3</v>
       </c>
       <c r="S10" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="T10" t="n">
-        <v>3.25</v>
+        <v>3.08</v>
       </c>
       <c r="U10" t="n">
         <v>2.36</v>
@@ -2024,25 +2024,25 @@
         <v>1.49</v>
       </c>
       <c r="W10" t="n">
-        <v>1.13</v>
+        <v>1.09</v>
       </c>
       <c r="X10" t="n">
         <v>1</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="Z10" t="n">
-        <v>4.1</v>
+        <v>4.05</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.42</v>
+        <v>2.63</v>
       </c>
       <c r="AD10" t="n">
         <v>1.43</v>
@@ -2051,10 +2051,10 @@
         <v>1.14</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="AG10" t="n">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2070,7 +2070,7 @@
         <v>1.24</v>
       </c>
       <c r="AK10" t="n">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2159,10 +2159,10 @@
         <v>2.91</v>
       </c>
       <c r="O11" t="n">
-        <v>2.93</v>
+        <v>2.8</v>
       </c>
       <c r="P11" t="n">
-        <v>2.55</v>
+        <v>2.35</v>
       </c>
       <c r="Q11" t="n">
         <v>3.45</v>
@@ -2171,43 +2171,43 @@
         <v>1.95</v>
       </c>
       <c r="S11" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="T11" t="n">
-        <v>2.36</v>
+        <v>2.44</v>
       </c>
       <c r="U11" t="n">
         <v>3.1</v>
       </c>
       <c r="V11" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="W11" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X11" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y11" t="n">
         <v>1.4</v>
       </c>
       <c r="Z11" t="n">
-        <v>2.63</v>
+        <v>2.8</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.3</v>
+        <v>2.19</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.5</v>
+        <v>1.65</v>
       </c>
       <c r="AC11" t="n">
-        <v>4.33</v>
+        <v>4</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="AF11" t="n">
         <v>1.85</v>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>

--- a/jogos_2026-06-01.xlsx
+++ b/jogos_2026-06-01.xlsx
@@ -1198,7 +1198,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N5" t="n">
@@ -1281,28 +1281,28 @@
         <v>0</v>
       </c>
       <c r="AM5" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AN5" t="n">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AO5" t="n">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AP5" t="n">
-        <v>-1</v>
+        <v>29</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0</v>
+        <v>0.76</v>
       </c>
       <c r="AR5" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AS5" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AT5" t="n">
-        <v>0</v>
+        <v>73</v>
       </c>
       <c r="AU5" s="3" t="n">
         <v>46174.79166666666</v>
@@ -1338,10 +1338,10 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -1350,14 +1350,14 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N6" t="n">
@@ -1422,12 +1422,12 @@
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['85']</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['61']</t>
         </is>
       </c>
       <c r="AJ6" t="n">
@@ -1440,28 +1440,28 @@
         <v>0</v>
       </c>
       <c r="AM6" t="n">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AN6" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AO6" t="n">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="AP6" t="n">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AQ6" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AR6" t="n">
-        <v>0</v>
+        <v>0.88</v>
       </c>
       <c r="AS6" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AT6" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AU6" s="3" t="n">
         <v>46174.79166666666</v>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Deportes Santa Cruz</t>
+          <t>Curicó Unido</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Copiapó</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,80 +1520,80 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>2.25</v>
+        <v>2.87</v>
       </c>
       <c r="O7" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="P7" t="n">
-        <v>3</v>
+        <v>2.19</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.67</v>
+        <v>3.5</v>
       </c>
       <c r="R7" t="n">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="S7" t="n">
-        <v>1.35</v>
+        <v>1.31</v>
       </c>
       <c r="T7" t="n">
-        <v>2.66</v>
+        <v>3.02</v>
       </c>
       <c r="U7" t="n">
-        <v>2.89</v>
+        <v>2.47</v>
       </c>
       <c r="V7" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="W7" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X7" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>3.92</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ7" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AK7" t="n">
         <v>1.34</v>
-      </c>
-      <c r="W7" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X7" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ7" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>1.6</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Barra do Garcas</t>
+          <t>Deportes Santa Cruz</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Copiapó</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,64 +1679,64 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1.92</v>
+        <v>2.25</v>
       </c>
       <c r="O8" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="P8" t="n">
-        <v>4.05</v>
+        <v>3</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.69</v>
+        <v>2.67</v>
       </c>
       <c r="R8" t="n">
-        <v>1.86</v>
+        <v>2.05</v>
       </c>
       <c r="S8" t="n">
-        <v>1.52</v>
+        <v>1.35</v>
       </c>
       <c r="T8" t="n">
-        <v>2.33</v>
+        <v>2.66</v>
       </c>
       <c r="U8" t="n">
-        <v>3.48</v>
+        <v>2.89</v>
       </c>
       <c r="V8" t="n">
-        <v>1.22</v>
+        <v>1.34</v>
       </c>
       <c r="W8" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X8" t="n">
         <v>1.04</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.49</v>
+        <v>3.04</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.5</v>
+        <v>1.98</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.5</v>
+        <v>1.74</v>
       </c>
       <c r="AC8" t="n">
-        <v>5</v>
+        <v>3.8</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.12</v>
+        <v>1.24</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="AF8" t="n">
-        <v>2.08</v>
+        <v>1.77</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.64</v>
+        <v>1.92</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.69</v>
+        <v>1.6</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Curicó Unido</t>
+          <t>Barra do Garcas</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,64 +1838,64 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>2.87</v>
+        <v>1.92</v>
       </c>
       <c r="O9" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="P9" t="n">
-        <v>2.19</v>
+        <v>4.05</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.5</v>
+        <v>2.69</v>
       </c>
       <c r="R9" t="n">
-        <v>2.15</v>
+        <v>1.86</v>
       </c>
       <c r="S9" t="n">
-        <v>1.31</v>
+        <v>1.52</v>
       </c>
       <c r="T9" t="n">
-        <v>3.02</v>
+        <v>2.33</v>
       </c>
       <c r="U9" t="n">
-        <v>2.47</v>
+        <v>3.48</v>
       </c>
       <c r="V9" t="n">
-        <v>1.45</v>
+        <v>1.22</v>
       </c>
       <c r="W9" t="n">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="X9" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.2</v>
+        <v>1.42</v>
       </c>
       <c r="Z9" t="n">
-        <v>3.92</v>
+        <v>2.49</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.68</v>
+        <v>2.5</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.06</v>
+        <v>1.5</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.88</v>
+        <v>5</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.38</v>
+        <v>1.12</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.12</v>
+        <v>1.02</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.52</v>
+        <v>2.08</v>
       </c>
       <c r="AG9" t="n">
-        <v>2.27</v>
+        <v>1.64</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.34</v>
+        <v>1.69</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1997,64 +1997,64 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="O10" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="P10" t="n">
-        <v>2.4</v>
+        <v>2.34</v>
       </c>
       <c r="Q10" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="R10" t="n">
         <v>2.3</v>
       </c>
       <c r="S10" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="T10" t="n">
-        <v>3.08</v>
+        <v>3.28</v>
       </c>
       <c r="U10" t="n">
-        <v>2.36</v>
+        <v>2.22</v>
       </c>
       <c r="V10" t="n">
-        <v>1.49</v>
+        <v>1.58</v>
       </c>
       <c r="W10" t="n">
-        <v>1.09</v>
+        <v>1.12</v>
       </c>
       <c r="X10" t="n">
         <v>1</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="Z10" t="n">
-        <v>4.05</v>
+        <v>5</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.63</v>
+        <v>1.49</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.14</v>
+        <v>2.3</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.63</v>
+        <v>2.27</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.43</v>
+        <v>1.56</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.14</v>
+        <v>1.19</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.52</v>
+        <v>1.44</v>
       </c>
       <c r="AG10" t="n">
-        <v>2.4</v>
+        <v>2.55</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="AK10" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2162,25 +2162,25 @@
         <v>2.8</v>
       </c>
       <c r="P11" t="n">
-        <v>2.35</v>
+        <v>2.22</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="R11" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="S11" t="n">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="T11" t="n">
-        <v>2.44</v>
+        <v>2.47</v>
       </c>
       <c r="U11" t="n">
-        <v>3.1</v>
+        <v>3.12</v>
       </c>
       <c r="V11" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="W11" t="n">
         <v>1.02</v>
@@ -2195,10 +2195,10 @@
         <v>2.8</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.19</v>
+        <v>2.15</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="AC11" t="n">
         <v>4</v>
@@ -2229,7 +2229,7 @@
         <v>1.33</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
